--- a/Sutphin_Curtailment_Call_List.xlsx
+++ b/Sutphin_Curtailment_Call_List.xlsx
@@ -17413,15 +17413,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="78" customWidth="1" min="5" max="5"/>
-    <col width="62" customWidth="1" min="6" max="6"/>
+    <col width="96" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17473,7 +17473,7 @@
     <row r="5">
       <c r="A5" s="24" t="inlineStr">
         <is>
-          <t>THE TWO CALLS THAT ARE WORTH MORE THAN ANY GENERATOR</t>
+          <t>THE TWO HIGHEST-LEVERAGE CALLS IN THE WHOLE EXERCISE</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr"/>
@@ -17490,7 +17490,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>CEO / Presidente-executiva</t>
+          <t>Presidente Executiva</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -17505,12 +17505,12 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Speaks for ~40 member companies. Source of the ~R$6bn CCEE passivo figure. Has publicly refused to forecast take-up: 'Não posso garantir aqui que haverá adesão de 100%, nem de 50%.'</t>
+          <t>In post since 2011; also VP of GWEC. On Portaria 140, 22 Jul 2026: "Hoje eu não sei dizer qual será o grau de adesão… essa será uma decisão individual de cada empresa." And on the mechanics: "não haverá depósito em conta. Os valores serão abatidos de algo que as empresas teriam que pagar à CCEE."</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>One call reaches the whole membership. She is also the person who knows which members are wavering.</t>
+          <t>One call reaches ~40 member companies. She has publicly said adhesion is uncertain and company-by-company — that sentence IS the opening line. She is also the person who knows who is wavering.</t>
         </is>
       </c>
     </row>
@@ -17542,14 +17542,14 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>PARTNER OR COMPETITOR. He has the classification data and the credibility; he does not have capital. That is a complementary pairing, and it is the single highest-value call on this sheet.</t>
+          <t>PARTNER OR COMPETITOR. He has the classification data and the credibility; he has no capital. Decide which he is before someone else does.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="24" t="inlineStr">
         <is>
-          <t>NAMED IN THE PUBLIC RECORD ON CURTAILMENT — these people have self-identified as caring</t>
+          <t>THE ABEEÓLICA BOARD ROSTER — each member company's own regulatory representative</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr"/>
@@ -17561,17 +17561,17 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Liu Aquino</t>
+          <t>(mandate Apr 2025 – Apr 2027)</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Echoenergia (Equatorial)</t>
+          <t>ABEEólica Conselho</t>
         </is>
       </c>
       <c r="D9" s="13" t="inlineStr">
@@ -17581,61 +17581,41 @@
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>Publicly: some plants at ~45% restriction, 'patamar que torna a operação insustentável'. Company is plaintiff in two of the twelve suits.</t>
+          <t>Presidenta Laura Cristina da Fonseca Porto (Neoenergia) · Fernando Elias Domingos Sé (Casa dos Ventos) · Bernardo Bezerra (Serena) · Francine Martins Pisni (Auren) · Leandro César Xavier de Carvalho (ENGIE) · Hugo Renato Anacleto Nunes (EDP) · Carolyne Muniz Dias (Voltalia) · Manoel de Andrade Lira Neto (Atlas) · Adelson Gomes Ferraz (Brennand) · Sandro Kiyoshi Yamamoto (Renova) · Sérgio Henrique Andrade de Azevedo (Dois A) · Gilberto Lourenço Feldman (PEC) · Thaisa Alcoforado de Almeida (EDF Power Solutions)</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>Already litigating — must actively choose to abandon.</t>
+          <t>This single page names the person at each member company who already owns this issue internally. It is the highest-yield contact source found anywhere in this research.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Bernardo Bezerra</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Diretor de Regulação e Inovação</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>Serena Energia</t>
-        </is>
-      </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>Ex-PSR. Writes publicly on cut classification (eixos, 13 Apr 2026, 'Curtailment: separando o joio do trigo').</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>The most technically credible regulatory director in the sector on precisely this issue.</t>
-        </is>
-      </c>
+      <c r="A10" s="24" t="inlineStr">
+        <is>
+          <t>THE CURTAILMENT OWNER AT EACH MAJOR GENERATOR — call these, not the CEO</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr"/>
+      <c r="C10" s="15" t="inlineStr"/>
+      <c r="D10" s="15" t="inlineStr"/>
+      <c r="E10" s="15" t="inlineStr"/>
+      <c r="F10" s="15" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Gabriel Mann</t>
+          <t>Fernando Elias Domingos Sé</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Diretor de Regulação</t>
+          <t>Diretor de Regulação e Comercialização</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Engie Brasil Energia</t>
+          <t>Casa dos Ventos</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -17645,29 +17625,29 @@
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>Quoted updating Engie's curtailment projection to 25% for 2025.</t>
+          <t>Former Presidente do Conselho da ABEEólica; currently Casa dos Ventos' ABEEólica board representative. Title is 2025-vintage and may now be split with Itamar Lessa (Diretor de Comercialização).</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>Engie discloses percentages but has never published an R$ figure.</t>
+          <t>Largest single holder of eligible claim in Brazil (18.8% of the pool). Privately held, so no analyst has done this work for them.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Gustavo Estrella</t>
+          <t>Priscila Rochinha Lino</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Diretora Regulatório e Planejamento Energético</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>CPFL Energia</t>
+          <t>Auren Energia</t>
         </is>
       </c>
       <c r="D12" s="13" t="inlineStr">
@@ -17677,137 +17657,157 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Quoted on the step-change: 'Na média do semestre, tivemos um curtailment de 8,6% no ano passado, e nesse começo de ano, 20,9%.'</t>
+          <t>The ONS/ANEEL/CCEE owner at Auren. Separately: "Auren projeta receber R$250 mi com ressarcimento por curtailment" — Agência iNFRA, 14 Nov 2025.</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>CPFL is the most transparent discloser — R$558m FY2025 lost revenue, 30.8% curtailment.</t>
+          <t>Auren has PUBLICLY PUT A NUMBER ON WHAT IT EXPECTS TO RECEIVE. That makes it the single best-quantified conversation available — you can open with their own figure.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Isabella Sene</t>
+          <t>Gabriel Mann dos Santos</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Regulatory lead</t>
+          <t>Diretor de Regulação, Estratégia e Comunicação</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>ABSOLAR</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>M</t>
+          <t>Engie Brasil Energia</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>H</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>Source of the R$2.8bn centralised-solar ACR figure for 2025. ABSOLAR has stated the manifestação de interesse does not itself waive existing suits.</t>
+          <t>Curtailment owner. CEO Eduardo Sattamini, NeoFeed 26 May 2026: "A Engie não deve investir em nova capacidade intermitente até termos uma visibilidade de que o sistema precisa dessa energia." ~17% of output cut.</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>The solar counterpart to ABEEólica.</t>
+          <t>Engie discloses curtailment only in percentages and has never published an R$ figure. The gap between what they know and what they say is the opening.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Francisco Silva</t>
+          <t>Cristiano de Lima Logrado</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Regulatory</t>
+          <t>Diretor de Regulação e Mercado</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>ABEEólica</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>M</t>
+          <t>Equatorial Energia</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>H</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>Source of the R$2.5bn non-reimbursable sobreoferta figure.</t>
+          <t>The ANEEL/ONS/CCEE operator for the whole group INCLUDING Echoenergia. Has signed formal group letters to ANEEL. CFO Leonardo Lima: curtailment costs ~R$900m, group evaluating divestments; 4Q25 525 GWh constrained-off at a 27.4% restriction rate.</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>Has already quantified the waived side.</t>
+          <t>One call covers both Equatorial and Echoenergia — and Echoenergia is already plaintiff in two of the twelve lawsuits.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Rui Altieri</t>
+          <t>Liu Aquino</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Chairman</t>
+          <t>Diretor-Presidente</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>APINE</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>M</t>
+          <t>Echoenergia</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>H</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>Put the 2025 cost of curtailment at R$6bn.</t>
+          <t>Elected Jan 2024. 51.4% solar curtailment — worst among the majors. NeoFeed 2 Oct 2025: "Os sinais econômicos do setor estão distorcidos diante desse cenário de curtailment da geração centralizada." Invited to testify at the Câmara dos Deputados hearing on curtailment, 17 Dec 2025.</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>Independent producers' association — reaches the mid-caps.</t>
+          <t>The most-quoted operator in Brazil on this issue, and already litigating. He has to actively choose to abandon those suits.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="24" t="inlineStr">
-        <is>
-          <t>REGULATORY AND OFFICIAL</t>
-        </is>
-      </c>
-      <c r="B16" s="15" t="inlineStr"/>
-      <c r="C16" s="15" t="inlineStr"/>
-      <c r="D16" s="15" t="inlineStr"/>
-      <c r="E16" s="15" t="inlineStr"/>
-      <c r="F16" s="15" t="inlineStr"/>
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Anna Paula Hiotte Pacheco</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Diretora de Regulação</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Enel Brasil</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>In role since Jul 2018 — eight years. Previously Diretora de Regulação Brasil e Uruguai at Enel Green Power Brasil. Sits on the boards of both ABEEólica and APINE.</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>Longest-tenured regulatory director in the set and sits on both association boards. Decision may still need Rome, but she is where it starts.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Agnes Maria de Aragão da Costa</t>
+          <t>Gustavo Andrioli</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Diretora</t>
+          <t>VP Sr. Jurídico, Regulatório e de Compliance</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>ANEEL</t>
+          <t>Elera Renováveis (Brookfield)</t>
         </is>
       </c>
       <c r="D17" s="13" t="inlineStr">
@@ -17817,41 +17817,61 @@
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>Authored the January 2026 medida cautelar suspending REN 1.030 reapurações (Processo 48500.000231/2026-56). Her voto is the authoritative source for the 46/41/13 classification split.</t>
+          <t>Combined GC and regulatory — a single call covers both. "Com 23% da geração cortada, Elera aguarda solução definitiva para o curtailment" — MegaWhat, 10 Nov 2025. CEO Karin Luchesi since May 2025; CFO José Simão.</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>Not a sales call. Read her voto before any regulatory conversation.</t>
+          <t>Elera holds an actual injunction (6ª Vara Federal DF, 18 Feb 2025, Complexo Alex, &gt;R$46m protected) — so it has the most to surrender by signing. Highest-stakes waiver decision in the market.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="24" t="inlineStr">
-        <is>
-          <t>ADVISERS ALREADY PUBLISHING ON PORTARIA 140</t>
-        </is>
-      </c>
-      <c r="B18" s="15" t="inlineStr"/>
-      <c r="C18" s="15" t="inlineStr"/>
-      <c r="D18" s="15" t="inlineStr"/>
-      <c r="E18" s="15" t="inlineStr"/>
-      <c r="F18" s="15" t="inlineStr"/>
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Solange Maria Pinto Ribeiro</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Diretora VP de Regulação, Institucional e Sustentabilidade</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Neoenergia (Iberdrola)</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>Curtailment owner — there is no standalone Diretor de Regulação. Note Neoenergia reorganised in April 2026: CFO+DRI is now Carlos Henrique Quadros Choqueta after Leonardo Gadelha resigned. Any contact list older than May 2026 is wrong.</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>Neoenergia is predominantly ACR/auction-contracted, so its compensation is more likely book entry than cash. Good advisory target, poor financing target.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Raphael Gomes</t>
+          <t>Hugo Renato Anacleto Nunes</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Partner, energy regulatory</t>
+          <t>Diretor Executivo de Regulação, EDP América do Sul</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Lefosse</t>
+          <t>EDP Brasil</t>
         </is>
       </c>
       <c r="D19" s="13" t="inlineStr">
@@ -17861,137 +17881,137 @@
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>Published a client alert on Portaria 140. Quoted: 'Com a tratativa atual, podemos ter mais uma onda de judicialização.'</t>
+          <t>Appointed 4 Dec 2025 — the freshest and most on-point contact in the set. Also EDP's ABEEólica board representative. Group president João Brito Martins since Jun 2025.</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>Already advising on this. Either a co-counsel or the competition — worth knowing which.</t>
+          <t>New in role, so still forming his position. EDP delisted in 2023 and has no active Brazilian IR function, which means no analyst is pressing them on this.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>(Mattos Filho energy team)</t>
+          <t>Rodrigo Limp Nascimento</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>VP Executivo de Regulação, Institucional e Mercado</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Mattos Filho</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>M</t>
+          <t>AXIA Energia (ex-Eletrobras)</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>H</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>Published a Portaria 140 client alert.</t>
+          <t>FORMER ANEEL DIRETOR-GERAL. Note the company rebranded from Eletrobras to AXIA — any list still saying Eletrobras is stale. Chesf, the Northeast entity, is led by Antonio Varejão de Godoy.</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>Same.</t>
+          <t>The highest-value regulatory call among the incumbents. He has sat on the other side of this exact rule. Not a sales call — an intelligence call.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="24" t="inlineStr">
-        <is>
-          <t>THINK TANKS AND CONSULTANCIES WITH PUBLISHED POSITIONS</t>
-        </is>
-      </c>
-      <c r="B21" s="15" t="inlineStr"/>
-      <c r="C21" s="15" t="inlineStr"/>
-      <c r="D21" s="15" t="inlineStr"/>
-      <c r="E21" s="15" t="inlineStr"/>
-      <c r="F21" s="15" t="inlineStr"/>
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>André Luiz Gomes da Silva</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>VP de Regulação e Mercado</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Copel</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>Appointed Nov 2024, term to 2026. Copel ran 37.4% wind curtailment in Q4 2025 per BTG.</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>Privatised in 2023, no controlling shareholder — decisions are commercial rather than political.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>Eduardo Müller Monteiro</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>Instituto Acende Brasil</t>
-        </is>
-      </c>
-      <c r="D22" s="13" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>Presented to the Senate CI hearing 30 Sep 2025. Best-documented independent methodology: R$3.85bn all cuts at PLD, R$2.85bn for the compensable subset.</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>The most rigorous public work on sizing. Read it before modelling.</t>
-        </is>
-      </c>
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>FINANCE — for when the conversation turns to the cash-versus-book-entry question</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr"/>
+      <c r="C22" s="15" t="inlineStr"/>
+      <c r="D22" s="15" t="inlineStr"/>
+      <c r="E22" s="15" t="inlineStr"/>
+      <c r="F22" s="15" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>João Carlos Mello</t>
+          <t>Andrea Sztajn</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Diretora Financeira e de Relações com Investidores</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Thymos Energia</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>M</t>
+          <t>Serena Energia</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>H</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>Argues PLD/CMO at R$200–300/MWh during oversupply is itself the distortion. Publishes no R$ tally.</t>
+          <t>CFO and DRI in one. At Omega/Serena since 2014; DRI since Sep 2024. Fitch: R$200m of 2025 EBITDA impact, 11% of total — the highest proportional hit of any rated name. Now controlled by Actis + GIC and delisting.</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>Useful on the price mechanics.</t>
+          <t>Serena is the most litigious name in the set — ANEEL denied its reclassification request in Feb 2025. She owns both the number and the decision.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Jean Paul Prates</t>
+          <t>Mateus Gomes Ferreira</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Chairman</t>
+          <t>VP de Finanças e Relações com Investidores</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Cerne</t>
+          <t>Auren Energia</t>
         </is>
       </c>
       <c r="D24" s="13" t="inlineStr">
@@ -18001,88 +18021,324 @@
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>Ex-Petrobras CEO. Cerne/CarpeVie put losses above R$5bn, 70% in the Nordeste.</t>
+          <t>Moved from Chairman to CFO+DRI on 1 Jul 2024. Has said publicly Auren has entered "a period of leverage stability" with deleveraging resuming only from 2027. FY2025 net loss R$557.9m; 1Q26 net loss R$601.6m; net debt/EBITDA back to 5.2x.</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>Political reach as much as technical.</t>
+          <t>Fitch revised Auren's outlook to Negative on 10 Jul 2026 citing curtailment at ~R$520m/year. The timing pressure is real and public.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="24" t="inlineStr">
-        <is>
-          <t>HOW TO USE THIS SHEET</t>
-        </is>
-      </c>
-      <c r="B25" s="15" t="inlineStr"/>
-      <c r="C25" s="15" t="inlineStr"/>
-      <c r="D25" s="15" t="inlineStr"/>
-      <c r="E25" s="15" t="inlineStr"/>
-      <c r="F25" s="15" t="inlineStr"/>
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Rafael Sanchez Brandão</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>CFO, DRI and Chairman</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>Rio Alto Energia</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>Holds all three roles. CAUTION: a CVM Termo de Compromisso was accepted in Oct 2024 against both him and CEO Edmond Chaker Farhat Junior. Know this before calling.</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>The one acute name — extrajudicial recovery extinguished June 2026, BTG enforcing Santa Luzia 5/7/9, sale mandated by end-2026, no buyer. It cannot survive to collect. Advisory only; this is not a lending situation.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>No email addresses are given here</t>
+          <t>Fernando Guedes Vieira</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
+          <t>Diretor Presidente, VP Jurídico e DRI</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>2W Ecobank</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>Elected 22 Apr 2026, mandate to 2029, covering four of the six relevant roles. IN RECUPERAÇÃO JUDICIAL — plan homologated by cram down Dec 2025, ~R$2.6bn. Judicial administrator: Vivante.</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>Your only contact there. Do NOT call from stale lists — Rolim, Coutinho, Pereira, Aguiar and Berenguer all departed in Apr 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>THE OTHER ASSOCIATION, AND THE REGIONAL VOICES</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="inlineStr"/>
+      <c r="C27" s="15" t="inlineStr"/>
+      <c r="D27" s="15" t="inlineStr"/>
+      <c r="E27" s="15" t="inlineStr"/>
+      <c r="F27" s="15" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Rodrigo Lopes Sauaia</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Presidente Executivo</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>ABSOLAR</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>Co-founder. Has warned repeatedly on judicialisation persisting after Portaria 140 (MegaWhat, 23 Jul 2026), and that MME gave no sufficiently clear criteria for classifying cut types. Superintendente: Celina Araújo.</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>The solar counterpart to Gannoum. ABSOLAR's public read — that the manifestação does not itself waive existing suits — is the one that matters most to our thesis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Isabella Sene</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Técnico e Regulatório (TECREG)</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>ABSOLAR</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>ABSOLAR publishes no 'diretor regulatório' title; regulatory work sits in the TECREG team. Source of the R$2.8bn centralised-solar ACR figure for 2025.</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>The working-level regulatory contact. NOTE: 'Talita Porto, Diretora Técnico-Regulatória' appears in search results but is NOT on the current staff page — do not use that name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Sérgio Azevedo / Darlan Santos</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Presidente, COERE-FIERN / Presidente, Cerne</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>Regional (RN)</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>Both warned publicly on 22 Jul 2026 that overgeneration cuts — the most recurrent in the Northeast — are expressly excluded, and that signing bars contesting the classification.</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>They have already made our central argument in public. Rio Grande do Norte is 44% of the eligible pool, so these are the right regional doors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>HOW TO USE THIS SHEET</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr"/>
+      <c r="C31" s="15" t="inlineStr"/>
+      <c r="D31" s="15" t="inlineStr"/>
+      <c r="E31" s="15" t="inlineStr"/>
+      <c r="F31" s="15" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Call the regulatory director, not the CEO</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D26" s="25" t="inlineStr">
+      <c r="D32" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>Every name above is sourced from a published quote, filing or IR page. NO EMAIL ADDRESS HAS BEEN CONSTRUCTED OR GUESSED — the Apollo database returned a billing error on this account, so nothing here comes from a contact database.</t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>Route in through GC's network rather than cold email. For the ones with no route, the association call (Gannoum, Sene) is the way in.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>Company CFOs and GCs are deliberately not listed</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>In almost every company above there is one named person who owns ONS/ANEEL/CCEE matters. That is who understands the classification question, and that is who will recognise within thirty seconds whether you have read the Termo or a law firm summary.</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>The CEO call comes second, after the regulatory director has validated that the question is real.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>No email addresses are constructed here</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D27" s="25" t="inlineStr">
+      <c r="D33" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>A separate agent was still searching IR pages and CVM filings when this was built. Rather than pad the sheet with guessed names, the roles are left for GC to fill from his own network — which is faster and more accurate than anything scraped.</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>The five names at the top of this sheet are enough to start.</t>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>Every name is from an official governance page, a CVM filing, or a published quote. NO EMAIL HAS BEEN BUILT FROM A PATTERN. Published department inboxes exist for Engie, Enel, Neoenergia, Voltalia, Rio Alto, Copel, Cemig and AXIA; the Apollo contact database returned a billing error on this account and was not used.</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>Route in through GC's network. Where there is no route, the association call is the way in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Confidence and staleness</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D34" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>H = on an official governance page or in a filing. M = published title but 2025-vintage or from a conference listing. Several companies reorganised recently — Neoenergia in Apr 2026, Engie Jul 2025, 2W Apr 2026, Eletrobras rebranded to AXIA. Verify the title before you use it in a first sentence.</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>A wrong title in the first sentence costs more than not knowing the name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Where nobody could be found</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D35" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>No name was found for: Casa dos Ventos CFO and GC; Serena regulatory and commercial directors; Voltalia Brasil CFO and regulatory; Rio Energy and Essentia entire boards; Furnas (site returns errors); Bolt, Newave, Solatio, Lightsource bp Brasil, Canadian Solar Brasil; and named partners at Pátria, Perfin, Prisma, Mubadala and BTG.</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>These are gaps, not absences. GC's network will close most of them faster than any search could.</t>
         </is>
       </c>
     </row>
@@ -18301,7 +18557,7 @@
     <row r="16">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>It does not value the garantia física loss</t>
+          <t>It does not value the garantia física BENEFIT</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr"/>

--- a/Sutphin_Curtailment_Call_List.xlsx
+++ b/Sutphin_Curtailment_Call_List.xlsx
@@ -8,12 +8,13 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Call List" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Complexes" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contacts" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portaria 140 - Mechanics" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Call Script" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PF Targets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Complexes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contacts" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portaria 140 - Mechanics" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Call Script" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,7 +28,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -106,6 +107,23 @@
     </font>
     <font>
       <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <color rgb="000563C1"/>
       <sz val="9"/>
     </font>
@@ -164,7 +182,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -222,6 +240,18 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
@@ -246,7 +276,7 @@
     <xf numFmtId="166" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2931,6 +2961,706 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="54" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="62" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>The lending list — Fitch's watch-listed project financings, against our claim data</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Two independent sources that agree: Fitch's published Rating Watch Negative list, and our own eligible-claim computation from raw ONS data. 5,414 GWh — 21.4% of the national pool — sits inside these.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="21" t="inlineStr">
+        <is>
+          <t>Fitch, 19 May 2026 — Brazilian Renewable Projects to Face Persistent Curtailment Headwinds:</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr"/>
+      <c r="C4" s="7" t="inlineStr"/>
+      <c r="D4" s="7" t="inlineStr"/>
+      <c r="E4" s="7" t="inlineStr"/>
+      <c r="F4" s="7" t="inlineStr"/>
+      <c r="G4" s="7" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>Fitch assumes NO curtailment compensation in any of these rating cases, on the stated basis that 'energetic-related curtailment does not qualify for compensation under existing regulatory rules.'</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr"/>
+      <c r="C5" s="7" t="inlineStr"/>
+      <c r="D5" s="7" t="inlineStr"/>
+      <c r="E5" s="7" t="inlineStr"/>
+      <c r="F5" s="7" t="inlineStr"/>
+      <c r="G5" s="7" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>That is the commercial opening. Every rand of compensation these vehicles actually collect is upside the rating does not currently give them credit for — and for a project running a 1.03x minimum DSCR, that is the difference between a downgrade and a stabilisation. It gives a project-finance CFO a reason to pay for this work that a healthy holdco does not have.</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr"/>
+      <c r="C6" s="7" t="inlineStr"/>
+      <c r="D6" s="7" t="inlineStr"/>
+      <c r="E6" s="7" t="inlineStr"/>
+      <c r="F6" s="7" t="inlineStr"/>
+      <c r="G6" s="7" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>The portfolio generated ~85% of projected levels in the 12 months to Aug 2025. Relief is not expected until the Graça Aranha transmission line around 2030.</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr"/>
+      <c r="C7" s="7" t="inlineStr"/>
+      <c r="D7" s="7" t="inlineStr"/>
+      <c r="E7" s="7" t="inlineStr"/>
+      <c r="F7" s="7" t="inlineStr"/>
+      <c r="G7" s="7" t="inlineStr"/>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Fitch entity</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Our matched complexes</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>UF</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Eligible GWh</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Est. claim (R$m)</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Rating and coverage detail</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Sponsor / SPEs</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Named contact</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Why this one</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Serra do Mel Holding / Vila Piauí 1 e 2</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>SERRA DO MEL A, B, II A, II B, C</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>RN</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>2981</v>
+      </c>
+      <c r="E10" s="11">
+        <f>IF(ISNUMBER(D10),D10*1000*Assumptions!$B$8/1000000,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>On Rating Watch Negative 22 Oct 2025. Vila Piauí 1 and Vila Piauí 2 are separately listed on the same watch.</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>SPEs: Vila Piauí 1 e 2 Empreendimentos; Ventos de Vila Ceará I/II; Sol Serra do Mel I/II. Group attribution unconfirmed — verify before calling.</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>Not established — this is the single largest gap in the research and the highest-value one to close.</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>THE BIGGEST PRIZE ON THE SHEET. The largest eligible claim in the country sits inside project financings Fitch has on negative watch. R$388m of claim against vehicles whose ratings assume they collect nothing. Find the sponsor first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Assuruá 4 e 5 Holding Energia</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>LARANJEIRAS, SERRA DO ASSURUÁ, GENTIO DO OURO I</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>788</v>
+      </c>
+      <c r="E11" s="11">
+        <f>IF(ISNUMBER(D11),D11*1000*Assumptions!$B$8/1000000,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>On Rating Watch Negative 22 Oct 2025.</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Assuruá 1/3/4/5 SPEs are Serena Energia. Serra do Assuruá (846 MW) is ENGIE and is a different complex — do not conflate. Laranjeiras carries CARGILL AGRÍCOLA as an equity holder (autoprodução).</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>Serena: Andrea Sztajn, Diretora Financeira e de RI. Engie: Gabriel Mann dos Santos, Diretor de Regulação.</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Two different sponsors inside one Fitch line item. The Cargill autoprodução element matters: self-production volume is not committed to CCEAR-D/CER, so it falls into the PLD cash tranche.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Asa Branca Holding</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>BRISA POTIGUAR I, ASA BRANCA</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>RN</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>322</v>
+      </c>
+      <c r="E12" s="11">
+        <f>IF(ISNUMBER(D12),D12*1000*Assumptions!$B$8/1000000,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>On Rating Watch Negative 22 Oct 2025.</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>ESSENTIA ENERGIA (Pátria Investimentos). Asa Branca Holding S.A. (CNPJ 09.359.927/0001-97) is a CVM issuer alongside Essentia PCHs S.A.</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>Gabriel Marinho de Farias — Diretor de Relações com Investidores, Essentia, AND VP Sênior de Infraestrutura at Pátria Investimentos. Elected 07/04/2025. Francisco Moya Reina is Diretor Presidente.</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>BEST-QUALIFIED TARGET ON THE SHEET. A Fitch-watched project financing, a named IR director who also sits at the sponsor, and a CVM-registered issuer that must disclose. Essentia has no dedicated CFO or regulatory director — Farias is the whole finance function.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Tupi Energias Renováveis</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Not matched to a complex name in ONS data — Tupi is a holding over 13 wind SPEs</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E13" s="11">
+        <f>IF(ISNUMBER(D13),D13*1000*Assumptions!$B$8/1000000,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>DOWNGRADED AA(bra) to AA-(bra), Negative Outlook, 26 Jan 2026. BRL 820m in two series (BRL 580m to Oct 2034; BRL 240m to Oct 2036). Curtailment 210.4 GWh in 2025 = 28% of projected output. Fitch applies a 15% generation haircut to 2030. MIN DSCR 1.03x, AVG 1.20x 2026–2033 — 'weak'. Cannot distribute below 1.25x.</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>Ibitu Energia, controlled by FIP Astra. CEO Paulo Abranches since Jun 2024.</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>Paulo Abranches, CEO, Ibitu Energia.</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>IBITU HAS ALREADY PUT A NUMBER ON THIS ITSELF. Its audited FY2025 accounts state 441,837 MWh cut, R$120.6m of impact, and that Lei 15.269/2025 'abre caminho para o ressarcimento de aproximadamente R$54,7 milhões'. They have done the work, they are covenant-compliant but cannot distribute, and they have quantified the claim. Start here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Central Fotovoltaica São Pedro IV</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Not separately identified in the eligible-claim ranking</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E14" s="11">
+        <f>IF(ISNUMBER(D14),D14*1000*Assumptions!$B$8/1000000,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>DOWNGRADED AAA(bra) to AA(bra), Rating Watch Negative, 16 Oct 2025. BRL 95.5m debentures to 2034. Net generation 43.4 GWh in operating year 6 = ~55% OF P-50. Grid restricting output ~33% per year through 2030. MINIMUM DSCR 0.49x, average 1.08x 2025–2034. NEGATIVE OPERATING CASH FLOW.</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>ENGIE Brasil Energia.</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>Gabriel Mann dos Santos, Diretor de Regulação, Estratégia e Comunicação, Engie Brasil.</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>THE MOST DISTRESSED SINGLE CREDIT DOCUMENTED. A 0.49x minimum DSCR and negative operating cash flow at a project owned by an investment-grade sponsor. Engie has never published an R$ curtailment figure. This is the clearest case anywhere of a vehicle that needs the compensation to work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Complexo Morrinhos Energias Renováveis</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>CAMPO FORMOSO (partial match — verify)</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>101</v>
+      </c>
+      <c r="E15" s="11">
+        <f>IF(ISNUMBER(D15),D15*1000*Assumptions!$B$8/1000000,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>Watch REMOVED and AAA(bra) affirmed Stable, 16 Apr 2026 — but ONLY because of a 100% Santander Brasil bank guarantee plus &gt;BRL 100m liquidity. Average DSCR is below 1.0x through 2027 on Fitch's own rating case. BRL 102.5m debentures to Dec 2027.</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>CGN Brasil Energia (China General Nuclear).</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>CGN Brasil statutory board: Mingzhu Li (Diretor Presidente), Wen Zhao (Diretor Financeiro). No regulatory director published.</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>THE COUNTER-EXAMPLE, and instructive. Sub-1.0x coverage survives only because a bank stands behind it. Every project on this list without a guarantee is exposed. Useful to cite on other calls.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Ventos de São Clemente Holding</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>SÃO CLEMENTE</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>88</v>
+      </c>
+      <c r="E16" s="11">
+        <f>IF(ISNUMBER(D16),D16*1000*Assumptions!$B$8/1000000,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>On Rating Watch Negative 22 Oct 2025.</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>Echoenergia (Equatorial Energia). SPEs: Ventos de São Clemente I–VII Energias Renováveis.</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>Cristiano de Lima Logrado — Diretor de Regulação e Mercado, Equatorial (covers Echoenergia). Liu Aquino — Diretor-Presidente, Echoenergia.</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>Echoenergia is already plaintiff in two of the twelve lawsuits, runs 51.4% solar curtailment, and Equatorial has said publicly it is evaluating divestments over a ~R$900m curtailment cost. Group-level claim across all Echoenergia complexes is 1,092 GWh.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Itarema Geração de Energia</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>ITAREMA V</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>95</v>
+      </c>
+      <c r="E17" s="11">
+        <f>IF(ISNUMBER(D17),D17*1000*Assumptions!$B$8/1000000,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>On Rating Watch Negative 22 Oct 2025.</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>SPEs: Eólica Itarema II and V S.A. Group attribution unconfirmed.</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>Not established.</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>Small in isolation. Worth a call only once a route is known.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Pirapora II Solar Holding</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>PIRAPORA 2</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>87</v>
+      </c>
+      <c r="E18" s="11">
+        <f>IF(ISNUMBER(D18),D18*1000*Assumptions!$B$8/1000000,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>On Rating Watch Negative 22 Oct 2025. Was rated AAA(bra).</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>Historically an EDF Renewables / Canadian Solar joint venture.</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>EDF: Thaisa Alcoforado de Almeida is EDF Power Solutions' ABEEólica board representative.</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>Minas Gerais solar. MG ran the highest state curtailment rate in the country in 2025 at 27.4% — worse than RN. Small claim but a live credit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Ventos de São Tito Holding · Ventos de São Tomé Holding · Voltalia São Miguel do Gostoso</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>No direct name match in the ONS complex list — these are holdcos over SPEs</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E19" s="11">
+        <f>IF(ISNUMBER(D19),D19*1000*Assumptions!$B$8/1000000,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>All three on Rating Watch Negative 22 Oct 2025.</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>São Tito is associated with Casa dos Ventos / the Araripe complex. São Miguel do Gostoso is Voltalia.</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>Voltalia: Nicolas Thouverez, Head of Latin America. Casa dos Ventos: Fernando Elias Domingos Sé, Diretor de Regulação e Comercialização.</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>VOLTALIA IS THE ONE COMPANY THAT HAS ALREADY BOOKED REAL MONEY — R$175m of curtailment ressarcimento recognised in Q2 2026 results, and CEO Robert Klein confirmed in Sep 2025 they were already pursuing compensation for exactly this window. Call them to learn how it actually worked, not to sell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>TOTAL matched</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr"/>
+      <c r="C20" s="15" t="inlineStr"/>
+      <c r="D20" s="17">
+        <f>SUM(D10:D19)</f>
+        <v/>
+      </c>
+      <c r="E20" s="17">
+        <f>SUM(E10:E19)</f>
+        <v/>
+      </c>
+      <c r="F20" s="15" t="inlineStr"/>
+      <c r="G20" s="15" t="inlineStr"/>
+      <c r="H20" s="15" t="inlineStr"/>
+      <c r="I20" s="15" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>Why this tab is the lending list</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>These are the vehicles that cannot wait. A project financing with a 1.03x minimum DSCR cannot distribute, cannot refinance, and cannot absorb an eighteen-month delay — and unlike a holdco it has no other business to cross-subsidise it. Casa dos Ventos raised US$1.1bn in June 2026 and needs nothing from us. These do.</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr"/>
+      <c r="D22" s="7" t="inlineStr"/>
+      <c r="E22" s="7" t="inlineStr"/>
+      <c r="F22" s="7" t="inlineStr"/>
+      <c r="G22" s="7" t="inlineStr"/>
+      <c r="H22" s="7" t="inlineStr"/>
+      <c r="I22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>The verification that makes it credible</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>This tab is built from two independent directions that agree: Fitch's published watch list, and our own eligible-claim computation from raw ONS half-hourly data. Neither knew about the other. 5,414 GWh of eligible claim — 21.4% of the national pool — sits inside financings Fitch has flagged.</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr"/>
+      <c r="D23" s="7" t="inlineStr"/>
+      <c r="E23" s="7" t="inlineStr"/>
+      <c r="F23" s="7" t="inlineStr"/>
+      <c r="G23" s="7" t="inlineStr"/>
+      <c r="H23" s="7" t="inlineStr"/>
+      <c r="I23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>The caveat on matching</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Fitch names holding companies; ONS names physical complexes. Several matches are by name similarity and are marked for verification. Tupi, São Tito, São Tomé and São Miguel do Gostoso could not be matched to a complex at all — the holdco names do not appear in ONS's registry. Confirm each one before using it.</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr"/>
+      <c r="D24" s="7" t="inlineStr"/>
+      <c r="E24" s="7" t="inlineStr"/>
+      <c r="F24" s="7" t="inlineStr"/>
+      <c r="G24" s="7" t="inlineStr"/>
+      <c r="H24" s="7" t="inlineStr"/>
+      <c r="I24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>What is missing and matters most</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>The sponsor behind the Serra do Mel and Vila Piauí cluster. It is the largest eligible claim in Brazil, it is on Fitch's watch list, and we have not established who controls it. That single question is worth more than any other outstanding item in this workbook.</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr"/>
+      <c r="D25" s="7" t="inlineStr"/>
+      <c r="E25" s="7" t="inlineStr"/>
+      <c r="F25" s="7" t="inlineStr"/>
+      <c r="G25" s="7" t="inlineStr"/>
+      <c r="H25" s="7" t="inlineStr"/>
+      <c r="I25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>A single-source warning</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Every R$ curtailment loss figure in Brazil — R$6.5bn for 2025, R$1.6bn for 2024, the R$2.7bn compensable estimate — traces back to one consultancy, Volt Robotics. Valor, XP, BTG and the trade press all re-publish the same study. That is concentration risk in the market's own understanding, and it is also why Volt is either the most valuable partner available or the most dangerous competitor.</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr"/>
+      <c r="D26" s="7" t="inlineStr"/>
+      <c r="E26" s="7" t="inlineStr"/>
+      <c r="F26" s="7" t="inlineStr"/>
+      <c r="G26" s="7" t="inlineStr"/>
+      <c r="H26" s="7" t="inlineStr"/>
+      <c r="I26" s="7" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:M272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3059,18 +3789,18 @@
           <t>H</t>
         </is>
       </c>
-      <c r="G5" s="21" t="n">
+      <c r="G5" s="25" t="n">
         <v>950.6</v>
       </c>
       <c r="H5" s="10">
         <f>G5/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I5" s="22">
+      <c r="I5" s="26">
         <f>G5*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J5" s="23" t="n">
+      <c r="J5" s="27" t="n">
         <v>176.9</v>
       </c>
       <c r="K5" s="10" t="n">
@@ -3114,18 +3844,18 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G6" s="21" t="n">
+      <c r="G6" s="25" t="n">
         <v>940.1</v>
       </c>
       <c r="H6" s="10">
         <f>G6/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I6" s="22">
+      <c r="I6" s="26">
         <f>G6*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J6" s="23" t="n">
+      <c r="J6" s="27" t="n">
         <v>217</v>
       </c>
       <c r="K6" s="10" t="n">
@@ -3169,18 +3899,18 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G7" s="21" t="n">
+      <c r="G7" s="25" t="n">
         <v>670.7</v>
       </c>
       <c r="H7" s="10">
         <f>G7/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I7" s="22">
+      <c r="I7" s="26">
         <f>G7*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J7" s="23" t="n">
+      <c r="J7" s="27" t="n">
         <v>248.6</v>
       </c>
       <c r="K7" s="10" t="n">
@@ -3224,18 +3954,18 @@
           <t>H</t>
         </is>
       </c>
-      <c r="G8" s="21" t="n">
+      <c r="G8" s="25" t="n">
         <v>628.2</v>
       </c>
       <c r="H8" s="10">
         <f>G8/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I8" s="22">
+      <c r="I8" s="26">
         <f>G8*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J8" s="23" t="n">
+      <c r="J8" s="27" t="n">
         <v>625.2</v>
       </c>
       <c r="K8" s="10" t="n">
@@ -3279,18 +4009,18 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G9" s="21" t="n">
+      <c r="G9" s="25" t="n">
         <v>581.4</v>
       </c>
       <c r="H9" s="10">
         <f>G9/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I9" s="22">
+      <c r="I9" s="26">
         <f>G9*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J9" s="23" t="n">
+      <c r="J9" s="27" t="n">
         <v>237.2</v>
       </c>
       <c r="K9" s="10" t="n">
@@ -3334,18 +4064,18 @@
           <t>H</t>
         </is>
       </c>
-      <c r="G10" s="21" t="n">
+      <c r="G10" s="25" t="n">
         <v>476.9</v>
       </c>
       <c r="H10" s="10">
         <f>G10/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I10" s="22">
+      <c r="I10" s="26">
         <f>G10*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J10" s="23" t="n">
+      <c r="J10" s="27" t="n">
         <v>226</v>
       </c>
       <c r="K10" s="10" t="n">
@@ -3389,18 +4119,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G11" s="21" t="n">
+      <c r="G11" s="25" t="n">
         <v>435.4</v>
       </c>
       <c r="H11" s="10">
         <f>G11/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I11" s="22">
+      <c r="I11" s="26">
         <f>G11*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J11" s="23" t="n">
+      <c r="J11" s="27" t="n">
         <v>35.9</v>
       </c>
       <c r="K11" s="10" t="n">
@@ -3440,18 +4170,18 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G12" s="21" t="n">
+      <c r="G12" s="25" t="n">
         <v>407.2</v>
       </c>
       <c r="H12" s="10">
         <f>G12/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I12" s="22">
+      <c r="I12" s="26">
         <f>G12*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J12" s="23" t="n">
+      <c r="J12" s="27" t="n">
         <v>197.1</v>
       </c>
       <c r="K12" s="10" t="n">
@@ -3495,18 +4225,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G13" s="21" t="n">
+      <c r="G13" s="25" t="n">
         <v>402</v>
       </c>
       <c r="H13" s="10">
         <f>G13/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I13" s="22">
+      <c r="I13" s="26">
         <f>G13*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J13" s="23" t="n">
+      <c r="J13" s="27" t="n">
         <v>45.1</v>
       </c>
       <c r="K13" s="10" t="n">
@@ -3546,18 +4276,18 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G14" s="21" t="n">
+      <c r="G14" s="25" t="n">
         <v>388.1</v>
       </c>
       <c r="H14" s="10">
         <f>G14/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I14" s="22">
+      <c r="I14" s="26">
         <f>G14*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J14" s="23" t="n">
+      <c r="J14" s="27" t="n">
         <v>370.1</v>
       </c>
       <c r="K14" s="10" t="n">
@@ -3601,18 +4331,18 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G15" s="21" t="n">
+      <c r="G15" s="25" t="n">
         <v>382.3</v>
       </c>
       <c r="H15" s="10">
         <f>G15/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I15" s="22">
+      <c r="I15" s="26">
         <f>G15*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J15" s="23" t="n">
+      <c r="J15" s="27" t="n">
         <v>270</v>
       </c>
       <c r="K15" s="10" t="n">
@@ -3656,18 +4386,18 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G16" s="21" t="n">
+      <c r="G16" s="25" t="n">
         <v>349.4</v>
       </c>
       <c r="H16" s="10">
         <f>G16/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I16" s="22">
+      <c r="I16" s="26">
         <f>G16*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J16" s="23" t="n">
+      <c r="J16" s="27" t="n">
         <v>228.7</v>
       </c>
       <c r="K16" s="10" t="n">
@@ -3711,18 +4441,18 @@
           <t>H</t>
         </is>
       </c>
-      <c r="G17" s="21" t="n">
+      <c r="G17" s="25" t="n">
         <v>325.9</v>
       </c>
       <c r="H17" s="10">
         <f>G17/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I17" s="22">
+      <c r="I17" s="26">
         <f>G17*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J17" s="23" t="n">
+      <c r="J17" s="27" t="n">
         <v>206.7</v>
       </c>
       <c r="K17" s="10" t="n">
@@ -3766,18 +4496,18 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G18" s="21" t="n">
+      <c r="G18" s="25" t="n">
         <v>321.9</v>
       </c>
       <c r="H18" s="10">
         <f>G18/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I18" s="22">
+      <c r="I18" s="26">
         <f>G18*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J18" s="23" t="n">
+      <c r="J18" s="27" t="n">
         <v>277.7</v>
       </c>
       <c r="K18" s="10" t="n">
@@ -3821,18 +4551,18 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G19" s="21" t="n">
+      <c r="G19" s="25" t="n">
         <v>312.5</v>
       </c>
       <c r="H19" s="10">
         <f>G19/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I19" s="22">
+      <c r="I19" s="26">
         <f>G19*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J19" s="23" t="n">
+      <c r="J19" s="27" t="n">
         <v>320.6</v>
       </c>
       <c r="K19" s="10" t="n">
@@ -3876,18 +4606,18 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G20" s="21" t="n">
+      <c r="G20" s="25" t="n">
         <v>285.6</v>
       </c>
       <c r="H20" s="10">
         <f>G20/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I20" s="22">
+      <c r="I20" s="26">
         <f>G20*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J20" s="23" t="n">
+      <c r="J20" s="27" t="n">
         <v>166.1</v>
       </c>
       <c r="K20" s="10" t="n">
@@ -3931,18 +4661,18 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G21" s="21" t="n">
+      <c r="G21" s="25" t="n">
         <v>283.3</v>
       </c>
       <c r="H21" s="10">
         <f>G21/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I21" s="22">
+      <c r="I21" s="26">
         <f>G21*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J21" s="23" t="n">
+      <c r="J21" s="27" t="n">
         <v>187.5</v>
       </c>
       <c r="K21" s="10" t="n">
@@ -3986,18 +4716,18 @@
           <t>H</t>
         </is>
       </c>
-      <c r="G22" s="21" t="n">
+      <c r="G22" s="25" t="n">
         <v>281.8</v>
       </c>
       <c r="H22" s="10">
         <f>G22/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I22" s="22">
+      <c r="I22" s="26">
         <f>G22*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J22" s="23" t="n">
+      <c r="J22" s="27" t="n">
         <v>288.1</v>
       </c>
       <c r="K22" s="10" t="n">
@@ -4041,18 +4771,18 @@
           <t>H</t>
         </is>
       </c>
-      <c r="G23" s="21" t="n">
+      <c r="G23" s="25" t="n">
         <v>279.6</v>
       </c>
       <c r="H23" s="10">
         <f>G23/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I23" s="22">
+      <c r="I23" s="26">
         <f>G23*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J23" s="23" t="n">
+      <c r="J23" s="27" t="n">
         <v>321.9</v>
       </c>
       <c r="K23" s="10" t="n">
@@ -4096,18 +4826,18 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G24" s="21" t="n">
+      <c r="G24" s="25" t="n">
         <v>256</v>
       </c>
       <c r="H24" s="10">
         <f>G24/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I24" s="22">
+      <c r="I24" s="26">
         <f>G24*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J24" s="23" t="n">
+      <c r="J24" s="27" t="n">
         <v>183.2</v>
       </c>
       <c r="K24" s="10" t="n">
@@ -4151,18 +4881,18 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G25" s="21" t="n">
+      <c r="G25" s="25" t="n">
         <v>253.4</v>
       </c>
       <c r="H25" s="10">
         <f>G25/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I25" s="22">
+      <c r="I25" s="26">
         <f>G25*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J25" s="23" t="n">
+      <c r="J25" s="27" t="n">
         <v>245.4</v>
       </c>
       <c r="K25" s="10" t="n">
@@ -4206,18 +4936,18 @@
           <t>H</t>
         </is>
       </c>
-      <c r="G26" s="21" t="n">
+      <c r="G26" s="25" t="n">
         <v>252.7</v>
       </c>
       <c r="H26" s="10">
         <f>G26/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I26" s="22">
+      <c r="I26" s="26">
         <f>G26*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J26" s="23" t="n">
+      <c r="J26" s="27" t="n">
         <v>81.59999999999999</v>
       </c>
       <c r="K26" s="10" t="n">
@@ -4261,18 +4991,18 @@
           <t>H</t>
         </is>
       </c>
-      <c r="G27" s="21" t="n">
+      <c r="G27" s="25" t="n">
         <v>252.3</v>
       </c>
       <c r="H27" s="10">
         <f>G27/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I27" s="22">
+      <c r="I27" s="26">
         <f>G27*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J27" s="23" t="n">
+      <c r="J27" s="27" t="n">
         <v>215.5</v>
       </c>
       <c r="K27" s="10" t="n">
@@ -4316,18 +5046,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G28" s="21" t="n">
+      <c r="G28" s="25" t="n">
         <v>242</v>
       </c>
       <c r="H28" s="10">
         <f>G28/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I28" s="22">
+      <c r="I28" s="26">
         <f>G28*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J28" s="23" t="n">
+      <c r="J28" s="27" t="n">
         <v>276</v>
       </c>
       <c r="K28" s="10" t="n">
@@ -4367,18 +5097,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G29" s="21" t="n">
+      <c r="G29" s="25" t="n">
         <v>240.6</v>
       </c>
       <c r="H29" s="10">
         <f>G29/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I29" s="22">
+      <c r="I29" s="26">
         <f>G29*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J29" s="23" t="n">
+      <c r="J29" s="27" t="n">
         <v>452.8</v>
       </c>
       <c r="K29" s="10" t="n">
@@ -4418,18 +5148,18 @@
           <t>H</t>
         </is>
       </c>
-      <c r="G30" s="21" t="n">
+      <c r="G30" s="25" t="n">
         <v>232.6</v>
       </c>
       <c r="H30" s="10">
         <f>G30/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I30" s="22">
+      <c r="I30" s="26">
         <f>G30*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J30" s="23" t="n">
+      <c r="J30" s="27" t="n">
         <v>209.6</v>
       </c>
       <c r="K30" s="10" t="n">
@@ -4473,18 +5203,18 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G31" s="21" t="n">
+      <c r="G31" s="25" t="n">
         <v>225.5</v>
       </c>
       <c r="H31" s="10">
         <f>G31/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I31" s="22">
+      <c r="I31" s="26">
         <f>G31*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J31" s="23" t="n">
+      <c r="J31" s="27" t="n">
         <v>97.09999999999999</v>
       </c>
       <c r="K31" s="10" t="n">
@@ -4528,18 +5258,18 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G32" s="21" t="n">
+      <c r="G32" s="25" t="n">
         <v>219.8</v>
       </c>
       <c r="H32" s="10">
         <f>G32/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I32" s="22">
+      <c r="I32" s="26">
         <f>G32*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J32" s="23" t="n">
+      <c r="J32" s="27" t="n">
         <v>254.3</v>
       </c>
       <c r="K32" s="10" t="n">
@@ -4583,18 +5313,18 @@
           <t>H</t>
         </is>
       </c>
-      <c r="G33" s="21" t="n">
+      <c r="G33" s="25" t="n">
         <v>209.8</v>
       </c>
       <c r="H33" s="10">
         <f>G33/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I33" s="22">
+      <c r="I33" s="26">
         <f>G33*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J33" s="23" t="n">
+      <c r="J33" s="27" t="n">
         <v>240.5</v>
       </c>
       <c r="K33" s="10" t="n">
@@ -4638,18 +5368,18 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G34" s="21" t="n">
+      <c r="G34" s="25" t="n">
         <v>207.5</v>
       </c>
       <c r="H34" s="10">
         <f>G34/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I34" s="22">
+      <c r="I34" s="26">
         <f>G34*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J34" s="23" t="n">
+      <c r="J34" s="27" t="n">
         <v>177.3</v>
       </c>
       <c r="K34" s="10" t="n">
@@ -4693,18 +5423,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G35" s="21" t="n">
+      <c r="G35" s="25" t="n">
         <v>206.3</v>
       </c>
       <c r="H35" s="10">
         <f>G35/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I35" s="22">
+      <c r="I35" s="26">
         <f>G35*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J35" s="23" t="n">
+      <c r="J35" s="27" t="n">
         <v>128.5</v>
       </c>
       <c r="K35" s="10" t="n">
@@ -4744,18 +5474,18 @@
           <t>H</t>
         </is>
       </c>
-      <c r="G36" s="21" t="n">
+      <c r="G36" s="25" t="n">
         <v>204.2</v>
       </c>
       <c r="H36" s="10">
         <f>G36/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I36" s="22">
+      <c r="I36" s="26">
         <f>G36*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J36" s="23" t="n">
+      <c r="J36" s="27" t="n">
         <v>243.7</v>
       </c>
       <c r="K36" s="10" t="n">
@@ -4799,18 +5529,18 @@
           <t>H</t>
         </is>
       </c>
-      <c r="G37" s="21" t="n">
+      <c r="G37" s="25" t="n">
         <v>202.7</v>
       </c>
       <c r="H37" s="10">
         <f>G37/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I37" s="22">
+      <c r="I37" s="26">
         <f>G37*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J37" s="23" t="n">
+      <c r="J37" s="27" t="n">
         <v>205.3</v>
       </c>
       <c r="K37" s="10" t="n">
@@ -4854,18 +5584,18 @@
           <t>H</t>
         </is>
       </c>
-      <c r="G38" s="21" t="n">
+      <c r="G38" s="25" t="n">
         <v>198.3</v>
       </c>
       <c r="H38" s="10">
         <f>G38/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I38" s="22">
+      <c r="I38" s="26">
         <f>G38*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J38" s="23" t="n">
+      <c r="J38" s="27" t="n">
         <v>275.8</v>
       </c>
       <c r="K38" s="10" t="n">
@@ -4909,18 +5639,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G39" s="21" t="n">
+      <c r="G39" s="25" t="n">
         <v>195.8</v>
       </c>
       <c r="H39" s="10">
         <f>G39/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I39" s="22">
+      <c r="I39" s="26">
         <f>G39*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J39" s="23" t="n">
+      <c r="J39" s="27" t="n">
         <v>107.9</v>
       </c>
       <c r="K39" s="10" t="n">
@@ -4964,18 +5694,18 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G40" s="21" t="n">
+      <c r="G40" s="25" t="n">
         <v>193.7</v>
       </c>
       <c r="H40" s="10">
         <f>G40/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I40" s="22">
+      <c r="I40" s="26">
         <f>G40*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J40" s="23" t="n">
+      <c r="J40" s="27" t="n">
         <v>126.9</v>
       </c>
       <c r="K40" s="10" t="n">
@@ -5019,18 +5749,18 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G41" s="21" t="n">
+      <c r="G41" s="25" t="n">
         <v>192.1</v>
       </c>
       <c r="H41" s="10">
         <f>G41/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I41" s="22">
+      <c r="I41" s="26">
         <f>G41*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J41" s="23" t="n">
+      <c r="J41" s="27" t="n">
         <v>135.8</v>
       </c>
       <c r="K41" s="10" t="n">
@@ -5074,18 +5804,18 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G42" s="21" t="n">
+      <c r="G42" s="25" t="n">
         <v>189.4</v>
       </c>
       <c r="H42" s="10">
         <f>G42/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I42" s="22">
+      <c r="I42" s="26">
         <f>G42*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J42" s="23" t="n">
+      <c r="J42" s="27" t="n">
         <v>312.6</v>
       </c>
       <c r="K42" s="10" t="n">
@@ -5129,18 +5859,18 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G43" s="21" t="n">
+      <c r="G43" s="25" t="n">
         <v>181.9</v>
       </c>
       <c r="H43" s="10">
         <f>G43/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I43" s="22">
+      <c r="I43" s="26">
         <f>G43*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J43" s="23" t="n">
+      <c r="J43" s="27" t="n">
         <v>132.2</v>
       </c>
       <c r="K43" s="10" t="n">
@@ -5184,18 +5914,18 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G44" s="21" t="n">
+      <c r="G44" s="25" t="n">
         <v>175.4</v>
       </c>
       <c r="H44" s="10">
         <f>G44/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I44" s="22">
+      <c r="I44" s="26">
         <f>G44*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J44" s="23" t="n">
+      <c r="J44" s="27" t="n">
         <v>139.5</v>
       </c>
       <c r="K44" s="10" t="n">
@@ -5239,18 +5969,18 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G45" s="21" t="n">
+      <c r="G45" s="25" t="n">
         <v>172.6</v>
       </c>
       <c r="H45" s="10">
         <f>G45/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I45" s="22">
+      <c r="I45" s="26">
         <f>G45*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J45" s="23" t="n">
+      <c r="J45" s="27" t="n">
         <v>216.3</v>
       </c>
       <c r="K45" s="10" t="n">
@@ -5294,18 +6024,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G46" s="21" t="n">
+      <c r="G46" s="25" t="n">
         <v>169.8</v>
       </c>
       <c r="H46" s="10">
         <f>G46/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I46" s="22">
+      <c r="I46" s="26">
         <f>G46*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J46" s="23" t="n">
+      <c r="J46" s="27" t="n">
         <v>105.1</v>
       </c>
       <c r="K46" s="10" t="n">
@@ -5349,18 +6079,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G47" s="21" t="n">
+      <c r="G47" s="25" t="n">
         <v>169.1</v>
       </c>
       <c r="H47" s="10">
         <f>G47/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I47" s="22">
+      <c r="I47" s="26">
         <f>G47*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J47" s="23" t="n">
+      <c r="J47" s="27" t="n">
         <v>101.5</v>
       </c>
       <c r="K47" s="10" t="n">
@@ -5400,18 +6130,18 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G48" s="21" t="n">
+      <c r="G48" s="25" t="n">
         <v>167.7</v>
       </c>
       <c r="H48" s="10">
         <f>G48/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I48" s="22">
+      <c r="I48" s="26">
         <f>G48*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J48" s="23" t="n">
+      <c r="J48" s="27" t="n">
         <v>183.6</v>
       </c>
       <c r="K48" s="10" t="n">
@@ -5455,18 +6185,18 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G49" s="21" t="n">
+      <c r="G49" s="25" t="n">
         <v>166.3</v>
       </c>
       <c r="H49" s="10">
         <f>G49/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I49" s="22">
+      <c r="I49" s="26">
         <f>G49*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J49" s="23" t="n">
+      <c r="J49" s="27" t="n">
         <v>71.40000000000001</v>
       </c>
       <c r="K49" s="10" t="n">
@@ -5510,18 +6240,18 @@
           <t>H</t>
         </is>
       </c>
-      <c r="G50" s="21" t="n">
+      <c r="G50" s="25" t="n">
         <v>160.6</v>
       </c>
       <c r="H50" s="10">
         <f>G50/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I50" s="22">
+      <c r="I50" s="26">
         <f>G50*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J50" s="23" t="n">
+      <c r="J50" s="27" t="n">
         <v>297.7</v>
       </c>
       <c r="K50" s="10" t="n">
@@ -5565,18 +6295,18 @@
           <t>H</t>
         </is>
       </c>
-      <c r="G51" s="21" t="n">
+      <c r="G51" s="25" t="n">
         <v>160.2</v>
       </c>
       <c r="H51" s="10">
         <f>G51/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I51" s="22">
+      <c r="I51" s="26">
         <f>G51*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J51" s="23" t="n">
+      <c r="J51" s="27" t="n">
         <v>114.5</v>
       </c>
       <c r="K51" s="10" t="n">
@@ -5620,18 +6350,18 @@
           <t>H</t>
         </is>
       </c>
-      <c r="G52" s="21" t="n">
+      <c r="G52" s="25" t="n">
         <v>159.4</v>
       </c>
       <c r="H52" s="10">
         <f>G52/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I52" s="22">
+      <c r="I52" s="26">
         <f>G52*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J52" s="23" t="n">
+      <c r="J52" s="27" t="n">
         <v>201.8</v>
       </c>
       <c r="K52" s="10" t="n">
@@ -5675,18 +6405,18 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G53" s="21" t="n">
+      <c r="G53" s="25" t="n">
         <v>158.3</v>
       </c>
       <c r="H53" s="10">
         <f>G53/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I53" s="22">
+      <c r="I53" s="26">
         <f>G53*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J53" s="23" t="n">
+      <c r="J53" s="27" t="n">
         <v>123</v>
       </c>
       <c r="K53" s="10" t="n">
@@ -5730,18 +6460,18 @@
           <t>H</t>
         </is>
       </c>
-      <c r="G54" s="21" t="n">
+      <c r="G54" s="25" t="n">
         <v>156.6</v>
       </c>
       <c r="H54" s="10">
         <f>G54/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I54" s="22">
+      <c r="I54" s="26">
         <f>G54*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J54" s="23" t="n">
+      <c r="J54" s="27" t="n">
         <v>211.9</v>
       </c>
       <c r="K54" s="10" t="n">
@@ -5785,18 +6515,18 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G55" s="21" t="n">
+      <c r="G55" s="25" t="n">
         <v>154.1</v>
       </c>
       <c r="H55" s="10">
         <f>G55/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I55" s="22">
+      <c r="I55" s="26">
         <f>G55*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J55" s="23" t="n">
+      <c r="J55" s="27" t="n">
         <v>124.5</v>
       </c>
       <c r="K55" s="10" t="n">
@@ -5840,18 +6570,18 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G56" s="21" t="n">
+      <c r="G56" s="25" t="n">
         <v>152.3</v>
       </c>
       <c r="H56" s="10">
         <f>G56/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I56" s="22">
+      <c r="I56" s="26">
         <f>G56*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J56" s="23" t="n">
+      <c r="J56" s="27" t="n">
         <v>105.5</v>
       </c>
       <c r="K56" s="10" t="n">
@@ -5895,18 +6625,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G57" s="21" t="n">
+      <c r="G57" s="25" t="n">
         <v>150.2</v>
       </c>
       <c r="H57" s="10">
         <f>G57/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I57" s="22">
+      <c r="I57" s="26">
         <f>G57*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J57" s="23" t="n">
+      <c r="J57" s="27" t="n">
         <v>384.5</v>
       </c>
       <c r="K57" s="10" t="n">
@@ -5946,18 +6676,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G58" s="21" t="n">
+      <c r="G58" s="25" t="n">
         <v>149.3</v>
       </c>
       <c r="H58" s="10">
         <f>G58/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I58" s="22">
+      <c r="I58" s="26">
         <f>G58*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J58" s="23" t="n">
+      <c r="J58" s="27" t="n">
         <v>15.9</v>
       </c>
       <c r="K58" s="10" t="n">
@@ -5997,18 +6727,18 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G59" s="21" t="n">
+      <c r="G59" s="25" t="n">
         <v>144.3</v>
       </c>
       <c r="H59" s="10">
         <f>G59/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I59" s="22">
+      <c r="I59" s="26">
         <f>G59*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J59" s="23" t="n">
+      <c r="J59" s="27" t="n">
         <v>98.40000000000001</v>
       </c>
       <c r="K59" s="10" t="n">
@@ -6052,18 +6782,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G60" s="21" t="n">
+      <c r="G60" s="25" t="n">
         <v>142.4</v>
       </c>
       <c r="H60" s="10">
         <f>G60/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I60" s="22">
+      <c r="I60" s="26">
         <f>G60*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J60" s="23" t="n">
+      <c r="J60" s="27" t="n">
         <v>100.5</v>
       </c>
       <c r="K60" s="10" t="n">
@@ -6107,18 +6837,18 @@
           <t>H</t>
         </is>
       </c>
-      <c r="G61" s="21" t="n">
+      <c r="G61" s="25" t="n">
         <v>141.7</v>
       </c>
       <c r="H61" s="10">
         <f>G61/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I61" s="22">
+      <c r="I61" s="26">
         <f>G61*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J61" s="23" t="n">
+      <c r="J61" s="27" t="n">
         <v>161.3</v>
       </c>
       <c r="K61" s="10" t="n">
@@ -6162,18 +6892,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G62" s="21" t="n">
+      <c r="G62" s="25" t="n">
         <v>137.7</v>
       </c>
       <c r="H62" s="10">
         <f>G62/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I62" s="22">
+      <c r="I62" s="26">
         <f>G62*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J62" s="23" t="n">
+      <c r="J62" s="27" t="n">
         <v>66.3</v>
       </c>
       <c r="K62" s="10" t="n">
@@ -6213,18 +6943,18 @@
           <t>H</t>
         </is>
       </c>
-      <c r="G63" s="21" t="n">
+      <c r="G63" s="25" t="n">
         <v>137.2</v>
       </c>
       <c r="H63" s="10">
         <f>G63/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I63" s="22">
+      <c r="I63" s="26">
         <f>G63*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J63" s="23" t="n">
+      <c r="J63" s="27" t="n">
         <v>104.3</v>
       </c>
       <c r="K63" s="10" t="n">
@@ -6268,18 +6998,18 @@
           <t>H</t>
         </is>
       </c>
-      <c r="G64" s="21" t="n">
+      <c r="G64" s="25" t="n">
         <v>136.7</v>
       </c>
       <c r="H64" s="10">
         <f>G64/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I64" s="22">
+      <c r="I64" s="26">
         <f>G64*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J64" s="23" t="n">
+      <c r="J64" s="27" t="n">
         <v>66.8</v>
       </c>
       <c r="K64" s="10" t="n">
@@ -6323,18 +7053,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G65" s="21" t="n">
+      <c r="G65" s="25" t="n">
         <v>136.3</v>
       </c>
       <c r="H65" s="10">
         <f>G65/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I65" s="22">
+      <c r="I65" s="26">
         <f>G65*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J65" s="23" t="n">
+      <c r="J65" s="27" t="n">
         <v>208.8</v>
       </c>
       <c r="K65" s="10" t="n">
@@ -6374,18 +7104,18 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G66" s="21" t="n">
+      <c r="G66" s="25" t="n">
         <v>128.5</v>
       </c>
       <c r="H66" s="10">
         <f>G66/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I66" s="22">
+      <c r="I66" s="26">
         <f>G66*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J66" s="23" t="n">
+      <c r="J66" s="27" t="n">
         <v>97.8</v>
       </c>
       <c r="K66" s="10" t="n">
@@ -6429,18 +7159,18 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G67" s="21" t="n">
+      <c r="G67" s="25" t="n">
         <v>127.8</v>
       </c>
       <c r="H67" s="10">
         <f>G67/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I67" s="22">
+      <c r="I67" s="26">
         <f>G67*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J67" s="23" t="n">
+      <c r="J67" s="27" t="n">
         <v>139.7</v>
       </c>
       <c r="K67" s="10" t="n">
@@ -6484,18 +7214,18 @@
           <t>H</t>
         </is>
       </c>
-      <c r="G68" s="21" t="n">
+      <c r="G68" s="25" t="n">
         <v>127.1</v>
       </c>
       <c r="H68" s="10">
         <f>G68/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I68" s="22">
+      <c r="I68" s="26">
         <f>G68*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J68" s="23" t="n">
+      <c r="J68" s="27" t="n">
         <v>141.5</v>
       </c>
       <c r="K68" s="10" t="n">
@@ -6539,18 +7269,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G69" s="21" t="n">
+      <c r="G69" s="25" t="n">
         <v>126</v>
       </c>
       <c r="H69" s="10">
         <f>G69/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I69" s="22">
+      <c r="I69" s="26">
         <f>G69*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J69" s="23" t="n">
+      <c r="J69" s="27" t="n">
         <v>249.3</v>
       </c>
       <c r="K69" s="10" t="n">
@@ -6590,18 +7320,18 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G70" s="21" t="n">
+      <c r="G70" s="25" t="n">
         <v>124.7</v>
       </c>
       <c r="H70" s="10">
         <f>G70/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I70" s="22">
+      <c r="I70" s="26">
         <f>G70*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J70" s="23" t="n">
+      <c r="J70" s="27" t="n">
         <v>151.2</v>
       </c>
       <c r="K70" s="10" t="n">
@@ -6645,18 +7375,18 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G71" s="21" t="n">
+      <c r="G71" s="25" t="n">
         <v>124.3</v>
       </c>
       <c r="H71" s="10">
         <f>G71/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I71" s="22">
+      <c r="I71" s="26">
         <f>G71*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J71" s="23" t="n">
+      <c r="J71" s="27" t="n">
         <v>67.40000000000001</v>
       </c>
       <c r="K71" s="10" t="n">
@@ -6700,18 +7430,18 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G72" s="21" t="n">
+      <c r="G72" s="25" t="n">
         <v>123.8</v>
       </c>
       <c r="H72" s="10">
         <f>G72/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I72" s="22">
+      <c r="I72" s="26">
         <f>G72*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J72" s="23" t="n">
+      <c r="J72" s="27" t="n">
         <v>201.7</v>
       </c>
       <c r="K72" s="10" t="n">
@@ -6755,18 +7485,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G73" s="21" t="n">
+      <c r="G73" s="25" t="n">
         <v>118.7</v>
       </c>
       <c r="H73" s="10">
         <f>G73/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I73" s="22">
+      <c r="I73" s="26">
         <f>G73*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J73" s="23" t="n">
+      <c r="J73" s="27" t="n">
         <v>54.4</v>
       </c>
       <c r="K73" s="10" t="n">
@@ -6806,18 +7536,18 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G74" s="21" t="n">
+      <c r="G74" s="25" t="n">
         <v>115.6</v>
       </c>
       <c r="H74" s="10">
         <f>G74/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I74" s="22">
+      <c r="I74" s="26">
         <f>G74*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J74" s="23" t="n">
+      <c r="J74" s="27" t="n">
         <v>306.8</v>
       </c>
       <c r="K74" s="10" t="n">
@@ -6861,18 +7591,18 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G75" s="21" t="n">
+      <c r="G75" s="25" t="n">
         <v>114.2</v>
       </c>
       <c r="H75" s="10">
         <f>G75/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I75" s="22">
+      <c r="I75" s="26">
         <f>G75*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J75" s="23" t="n">
+      <c r="J75" s="27" t="n">
         <v>128.4</v>
       </c>
       <c r="K75" s="10" t="n">
@@ -6916,18 +7646,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G76" s="21" t="n">
+      <c r="G76" s="25" t="n">
         <v>113.5</v>
       </c>
       <c r="H76" s="10">
         <f>G76/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I76" s="22">
+      <c r="I76" s="26">
         <f>G76*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J76" s="23" t="n">
+      <c r="J76" s="27" t="n">
         <v>62.8</v>
       </c>
       <c r="K76" s="10" t="n">
@@ -6971,18 +7701,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G77" s="21" t="n">
+      <c r="G77" s="25" t="n">
         <v>113.1</v>
       </c>
       <c r="H77" s="10">
         <f>G77/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I77" s="22">
+      <c r="I77" s="26">
         <f>G77*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J77" s="23" t="n">
+      <c r="J77" s="27" t="n">
         <v>99.3</v>
       </c>
       <c r="K77" s="10" t="n">
@@ -7026,18 +7756,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G78" s="21" t="n">
+      <c r="G78" s="25" t="n">
         <v>113</v>
       </c>
       <c r="H78" s="10">
         <f>G78/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I78" s="22">
+      <c r="I78" s="26">
         <f>G78*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J78" s="23" t="n">
+      <c r="J78" s="27" t="n">
         <v>165.3</v>
       </c>
       <c r="K78" s="10" t="n">
@@ -7081,18 +7811,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G79" s="21" t="n">
+      <c r="G79" s="25" t="n">
         <v>110.9</v>
       </c>
       <c r="H79" s="10">
         <f>G79/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I79" s="22">
+      <c r="I79" s="26">
         <f>G79*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J79" s="23" t="n">
+      <c r="J79" s="27" t="n">
         <v>73.40000000000001</v>
       </c>
       <c r="K79" s="10" t="n">
@@ -7136,18 +7866,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G80" s="21" t="n">
+      <c r="G80" s="25" t="n">
         <v>110.2</v>
       </c>
       <c r="H80" s="10">
         <f>G80/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I80" s="22">
+      <c r="I80" s="26">
         <f>G80*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J80" s="23" t="n">
+      <c r="J80" s="27" t="n">
         <v>110.1</v>
       </c>
       <c r="K80" s="10" t="n">
@@ -7191,18 +7921,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G81" s="21" t="n">
+      <c r="G81" s="25" t="n">
         <v>110.1</v>
       </c>
       <c r="H81" s="10">
         <f>G81/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I81" s="22">
+      <c r="I81" s="26">
         <f>G81*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J81" s="23" t="n">
+      <c r="J81" s="27" t="n">
         <v>60</v>
       </c>
       <c r="K81" s="10" t="n">
@@ -7246,18 +7976,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G82" s="21" t="n">
+      <c r="G82" s="25" t="n">
         <v>109.7</v>
       </c>
       <c r="H82" s="10">
         <f>G82/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I82" s="22">
+      <c r="I82" s="26">
         <f>G82*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J82" s="23" t="n">
+      <c r="J82" s="27" t="n">
         <v>81.2</v>
       </c>
       <c r="K82" s="10" t="n">
@@ -7301,18 +8031,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G83" s="21" t="n">
+      <c r="G83" s="25" t="n">
         <v>108.8</v>
       </c>
       <c r="H83" s="10">
         <f>G83/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I83" s="22">
+      <c r="I83" s="26">
         <f>G83*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J83" s="23" t="n">
+      <c r="J83" s="27" t="n">
         <v>119.8</v>
       </c>
       <c r="K83" s="10" t="n">
@@ -7356,18 +8086,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G84" s="21" t="n">
+      <c r="G84" s="25" t="n">
         <v>106.3</v>
       </c>
       <c r="H84" s="10">
         <f>G84/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I84" s="22">
+      <c r="I84" s="26">
         <f>G84*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J84" s="23" t="n">
+      <c r="J84" s="27" t="n">
         <v>35.6</v>
       </c>
       <c r="K84" s="10" t="n">
@@ -7411,18 +8141,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G85" s="21" t="n">
+      <c r="G85" s="25" t="n">
         <v>105.1</v>
       </c>
       <c r="H85" s="10">
         <f>G85/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I85" s="22">
+      <c r="I85" s="26">
         <f>G85*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J85" s="23" t="n">
+      <c r="J85" s="27" t="n">
         <v>66</v>
       </c>
       <c r="K85" s="10" t="n">
@@ -7462,18 +8192,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G86" s="21" t="n">
+      <c r="G86" s="25" t="n">
         <v>102.2</v>
       </c>
       <c r="H86" s="10">
         <f>G86/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I86" s="22">
+      <c r="I86" s="26">
         <f>G86*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J86" s="23" t="n">
+      <c r="J86" s="27" t="n">
         <v>65</v>
       </c>
       <c r="K86" s="10" t="n">
@@ -7517,18 +8247,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G87" s="21" t="n">
+      <c r="G87" s="25" t="n">
         <v>101.3</v>
       </c>
       <c r="H87" s="10">
         <f>G87/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I87" s="22">
+      <c r="I87" s="26">
         <f>G87*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J87" s="23" t="n">
+      <c r="J87" s="27" t="n">
         <v>83.8</v>
       </c>
       <c r="K87" s="10" t="n">
@@ -7572,18 +8302,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G88" s="21" t="n">
+      <c r="G88" s="25" t="n">
         <v>99.90000000000001</v>
       </c>
       <c r="H88" s="10">
         <f>G88/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I88" s="22">
+      <c r="I88" s="26">
         <f>G88*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J88" s="23" t="n">
+      <c r="J88" s="27" t="n">
         <v>166.4</v>
       </c>
       <c r="K88" s="10" t="n">
@@ -7627,18 +8357,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G89" s="21" t="n">
+      <c r="G89" s="25" t="n">
         <v>98.2</v>
       </c>
       <c r="H89" s="10">
         <f>G89/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I89" s="22">
+      <c r="I89" s="26">
         <f>G89*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J89" s="23" t="n">
+      <c r="J89" s="27" t="n">
         <v>160.3</v>
       </c>
       <c r="K89" s="10" t="n">
@@ -7678,18 +8408,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G90" s="21" t="n">
+      <c r="G90" s="25" t="n">
         <v>96.8</v>
       </c>
       <c r="H90" s="10">
         <f>G90/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I90" s="22">
+      <c r="I90" s="26">
         <f>G90*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J90" s="23" t="n">
+      <c r="J90" s="27" t="n">
         <v>144.2</v>
       </c>
       <c r="K90" s="10" t="n">
@@ -7733,18 +8463,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G91" s="21" t="n">
+      <c r="G91" s="25" t="n">
         <v>96.59999999999999</v>
       </c>
       <c r="H91" s="10">
         <f>G91/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I91" s="22">
+      <c r="I91" s="26">
         <f>G91*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J91" s="23" t="n">
+      <c r="J91" s="27" t="n">
         <v>104.1</v>
       </c>
       <c r="K91" s="10" t="n">
@@ -7788,18 +8518,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G92" s="21" t="n">
+      <c r="G92" s="25" t="n">
         <v>95.2</v>
       </c>
       <c r="H92" s="10">
         <f>G92/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I92" s="22">
+      <c r="I92" s="26">
         <f>G92*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J92" s="23" t="n">
+      <c r="J92" s="27" t="n">
         <v>153</v>
       </c>
       <c r="K92" s="10" t="n">
@@ -7843,18 +8573,18 @@
           <t>H</t>
         </is>
       </c>
-      <c r="G93" s="21" t="n">
+      <c r="G93" s="25" t="n">
         <v>94.5</v>
       </c>
       <c r="H93" s="10">
         <f>G93/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I93" s="22">
+      <c r="I93" s="26">
         <f>G93*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J93" s="23" t="n">
+      <c r="J93" s="27" t="n">
         <v>50.4</v>
       </c>
       <c r="K93" s="10" t="n">
@@ -7898,18 +8628,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G94" s="21" t="n">
+      <c r="G94" s="25" t="n">
         <v>93.5</v>
       </c>
       <c r="H94" s="10">
         <f>G94/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I94" s="22">
+      <c r="I94" s="26">
         <f>G94*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J94" s="23" t="n">
+      <c r="J94" s="27" t="n">
         <v>56.7</v>
       </c>
       <c r="K94" s="10" t="n">
@@ -7949,18 +8679,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G95" s="21" t="n">
+      <c r="G95" s="25" t="n">
         <v>92.7</v>
       </c>
       <c r="H95" s="10">
         <f>G95/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I95" s="22">
+      <c r="I95" s="26">
         <f>G95*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J95" s="23" t="n">
+      <c r="J95" s="27" t="n">
         <v>160.2</v>
       </c>
       <c r="K95" s="10" t="n">
@@ -8004,18 +8734,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G96" s="21" t="n">
+      <c r="G96" s="25" t="n">
         <v>92.59999999999999</v>
       </c>
       <c r="H96" s="10">
         <f>G96/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I96" s="22">
+      <c r="I96" s="26">
         <f>G96*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J96" s="23" t="n">
+      <c r="J96" s="27" t="n">
         <v>98.5</v>
       </c>
       <c r="K96" s="10" t="n">
@@ -8059,18 +8789,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G97" s="21" t="n">
+      <c r="G97" s="25" t="n">
         <v>89.59999999999999</v>
       </c>
       <c r="H97" s="10">
         <f>G97/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I97" s="22">
+      <c r="I97" s="26">
         <f>G97*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J97" s="23" t="n">
+      <c r="J97" s="27" t="n">
         <v>158.3</v>
       </c>
       <c r="K97" s="10" t="n">
@@ -8114,18 +8844,18 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G98" s="21" t="n">
+      <c r="G98" s="25" t="n">
         <v>88.8</v>
       </c>
       <c r="H98" s="10">
         <f>G98/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I98" s="22">
+      <c r="I98" s="26">
         <f>G98*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J98" s="23" t="n">
+      <c r="J98" s="27" t="n">
         <v>72.09999999999999</v>
       </c>
       <c r="K98" s="10" t="n">
@@ -8169,18 +8899,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G99" s="21" t="n">
+      <c r="G99" s="25" t="n">
         <v>87.90000000000001</v>
       </c>
       <c r="H99" s="10">
         <f>G99/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I99" s="22">
+      <c r="I99" s="26">
         <f>G99*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J99" s="23" t="n">
+      <c r="J99" s="27" t="n">
         <v>113.5</v>
       </c>
       <c r="K99" s="10" t="n">
@@ -8224,18 +8954,18 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G100" s="21" t="n">
+      <c r="G100" s="25" t="n">
         <v>87.8</v>
       </c>
       <c r="H100" s="10">
         <f>G100/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I100" s="22">
+      <c r="I100" s="26">
         <f>G100*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J100" s="23" t="n">
+      <c r="J100" s="27" t="n">
         <v>109.4</v>
       </c>
       <c r="K100" s="10" t="n">
@@ -8279,18 +9009,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G101" s="21" t="n">
+      <c r="G101" s="25" t="n">
         <v>86.5</v>
       </c>
       <c r="H101" s="10">
         <f>G101/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I101" s="22">
+      <c r="I101" s="26">
         <f>G101*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J101" s="23" t="n">
+      <c r="J101" s="27" t="n">
         <v>162</v>
       </c>
       <c r="K101" s="10" t="n">
@@ -8334,18 +9064,18 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G102" s="21" t="n">
+      <c r="G102" s="25" t="n">
         <v>85.59999999999999</v>
       </c>
       <c r="H102" s="10">
         <f>G102/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I102" s="22">
+      <c r="I102" s="26">
         <f>G102*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J102" s="23" t="n">
+      <c r="J102" s="27" t="n">
         <v>43.9</v>
       </c>
       <c r="K102" s="10" t="n">
@@ -8389,18 +9119,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G103" s="21" t="n">
+      <c r="G103" s="25" t="n">
         <v>85.09999999999999</v>
       </c>
       <c r="H103" s="10">
         <f>G103/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I103" s="22">
+      <c r="I103" s="26">
         <f>G103*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J103" s="23" t="n">
+      <c r="J103" s="27" t="n">
         <v>80.3</v>
       </c>
       <c r="K103" s="10" t="n">
@@ -8444,18 +9174,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G104" s="21" t="n">
+      <c r="G104" s="25" t="n">
         <v>83</v>
       </c>
       <c r="H104" s="10">
         <f>G104/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I104" s="22">
+      <c r="I104" s="26">
         <f>G104*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J104" s="23" t="n">
+      <c r="J104" s="27" t="n">
         <v>54.2</v>
       </c>
       <c r="K104" s="10" t="n">
@@ -8499,18 +9229,18 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G105" s="21" t="n">
+      <c r="G105" s="25" t="n">
         <v>82.7</v>
       </c>
       <c r="H105" s="10">
         <f>G105/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I105" s="22">
+      <c r="I105" s="26">
         <f>G105*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J105" s="23" t="n">
+      <c r="J105" s="27" t="n">
         <v>59.8</v>
       </c>
       <c r="K105" s="10" t="n">
@@ -8554,18 +9284,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G106" s="21" t="n">
+      <c r="G106" s="25" t="n">
         <v>78.8</v>
       </c>
       <c r="H106" s="10">
         <f>G106/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I106" s="22">
+      <c r="I106" s="26">
         <f>G106*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J106" s="23" t="n">
+      <c r="J106" s="27" t="n">
         <v>90.59999999999999</v>
       </c>
       <c r="K106" s="10" t="n">
@@ -8609,18 +9339,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G107" s="21" t="n">
+      <c r="G107" s="25" t="n">
         <v>78.2</v>
       </c>
       <c r="H107" s="10">
         <f>G107/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I107" s="22">
+      <c r="I107" s="26">
         <f>G107*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J107" s="23" t="n">
+      <c r="J107" s="27" t="n">
         <v>49.1</v>
       </c>
       <c r="K107" s="10" t="n">
@@ -8664,18 +9394,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G108" s="21" t="n">
+      <c r="G108" s="25" t="n">
         <v>78.2</v>
       </c>
       <c r="H108" s="10">
         <f>G108/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I108" s="22">
+      <c r="I108" s="26">
         <f>G108*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J108" s="23" t="n">
+      <c r="J108" s="27" t="n">
         <v>35</v>
       </c>
       <c r="K108" s="10" t="n">
@@ -8719,18 +9449,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G109" s="21" t="n">
+      <c r="G109" s="25" t="n">
         <v>78.09999999999999</v>
       </c>
       <c r="H109" s="10">
         <f>G109/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I109" s="22">
+      <c r="I109" s="26">
         <f>G109*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J109" s="23" t="n">
+      <c r="J109" s="27" t="n">
         <v>38.2</v>
       </c>
       <c r="K109" s="10" t="n">
@@ -8774,18 +9504,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G110" s="21" t="n">
+      <c r="G110" s="25" t="n">
         <v>75.7</v>
       </c>
       <c r="H110" s="10">
         <f>G110/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I110" s="22">
+      <c r="I110" s="26">
         <f>G110*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J110" s="23" t="n">
+      <c r="J110" s="27" t="n">
         <v>40.4</v>
       </c>
       <c r="K110" s="10" t="n">
@@ -8829,18 +9559,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G111" s="21" t="n">
+      <c r="G111" s="25" t="n">
         <v>73.59999999999999</v>
       </c>
       <c r="H111" s="10">
         <f>G111/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I111" s="22">
+      <c r="I111" s="26">
         <f>G111*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J111" s="23" t="n">
+      <c r="J111" s="27" t="n">
         <v>48.1</v>
       </c>
       <c r="K111" s="10" t="n">
@@ -8880,18 +9610,18 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G112" s="21" t="n">
+      <c r="G112" s="25" t="n">
         <v>72.2</v>
       </c>
       <c r="H112" s="10">
         <f>G112/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I112" s="22">
+      <c r="I112" s="26">
         <f>G112*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J112" s="23" t="n">
+      <c r="J112" s="27" t="n">
         <v>106.1</v>
       </c>
       <c r="K112" s="10" t="n">
@@ -8935,18 +9665,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G113" s="21" t="n">
+      <c r="G113" s="25" t="n">
         <v>72.09999999999999</v>
       </c>
       <c r="H113" s="10">
         <f>G113/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I113" s="22">
+      <c r="I113" s="26">
         <f>G113*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J113" s="23" t="n">
+      <c r="J113" s="27" t="n">
         <v>47.4</v>
       </c>
       <c r="K113" s="10" t="n">
@@ -8990,18 +9720,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G114" s="21" t="n">
+      <c r="G114" s="25" t="n">
         <v>70.59999999999999</v>
       </c>
       <c r="H114" s="10">
         <f>G114/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I114" s="22">
+      <c r="I114" s="26">
         <f>G114*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J114" s="23" t="n">
+      <c r="J114" s="27" t="n">
         <v>46.6</v>
       </c>
       <c r="K114" s="10" t="n">
@@ -9045,18 +9775,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G115" s="21" t="n">
+      <c r="G115" s="25" t="n">
         <v>70.5</v>
       </c>
       <c r="H115" s="10">
         <f>G115/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I115" s="22">
+      <c r="I115" s="26">
         <f>G115*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J115" s="23" t="n">
+      <c r="J115" s="27" t="n">
         <v>141.4</v>
       </c>
       <c r="K115" s="10" t="n">
@@ -9100,18 +9830,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G116" s="21" t="n">
+      <c r="G116" s="25" t="n">
         <v>69.3</v>
       </c>
       <c r="H116" s="10">
         <f>G116/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I116" s="22">
+      <c r="I116" s="26">
         <f>G116*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J116" s="23" t="n">
+      <c r="J116" s="27" t="n">
         <v>40.4</v>
       </c>
       <c r="K116" s="10" t="n">
@@ -9151,18 +9881,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G117" s="21" t="n">
+      <c r="G117" s="25" t="n">
         <v>68.90000000000001</v>
       </c>
       <c r="H117" s="10">
         <f>G117/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I117" s="22">
+      <c r="I117" s="26">
         <f>G117*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J117" s="23" t="n">
+      <c r="J117" s="27" t="n">
         <v>85.59999999999999</v>
       </c>
       <c r="K117" s="10" t="n">
@@ -9206,18 +9936,18 @@
           <t>H</t>
         </is>
       </c>
-      <c r="G118" s="21" t="n">
+      <c r="G118" s="25" t="n">
         <v>67.59999999999999</v>
       </c>
       <c r="H118" s="10">
         <f>G118/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I118" s="22">
+      <c r="I118" s="26">
         <f>G118*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J118" s="23" t="n">
+      <c r="J118" s="27" t="n">
         <v>40.2</v>
       </c>
       <c r="K118" s="10" t="n">
@@ -9261,18 +9991,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G119" s="21" t="n">
+      <c r="G119" s="25" t="n">
         <v>67</v>
       </c>
       <c r="H119" s="10">
         <f>G119/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I119" s="22">
+      <c r="I119" s="26">
         <f>G119*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J119" s="23" t="n">
+      <c r="J119" s="27" t="n">
         <v>41.4</v>
       </c>
       <c r="K119" s="10" t="n">
@@ -9312,18 +10042,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G120" s="21" t="n">
+      <c r="G120" s="25" t="n">
         <v>66.59999999999999</v>
       </c>
       <c r="H120" s="10">
         <f>G120/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I120" s="22">
+      <c r="I120" s="26">
         <f>G120*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J120" s="23" t="n">
+      <c r="J120" s="27" t="n">
         <v>40.4</v>
       </c>
       <c r="K120" s="10" t="n">
@@ -9363,18 +10093,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G121" s="21" t="n">
+      <c r="G121" s="25" t="n">
         <v>66.2</v>
       </c>
       <c r="H121" s="10">
         <f>G121/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I121" s="22">
+      <c r="I121" s="26">
         <f>G121*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J121" s="23" t="n">
+      <c r="J121" s="27" t="n">
         <v>60.3</v>
       </c>
       <c r="K121" s="10" t="n">
@@ -9418,18 +10148,18 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G122" s="21" t="n">
+      <c r="G122" s="25" t="n">
         <v>65.3</v>
       </c>
       <c r="H122" s="10">
         <f>G122/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I122" s="22">
+      <c r="I122" s="26">
         <f>G122*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J122" s="23" t="n">
+      <c r="J122" s="27" t="n">
         <v>142.5</v>
       </c>
       <c r="K122" s="10" t="n">
@@ -9473,18 +10203,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G123" s="21" t="n">
+      <c r="G123" s="25" t="n">
         <v>64.5</v>
       </c>
       <c r="H123" s="10">
         <f>G123/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I123" s="22">
+      <c r="I123" s="26">
         <f>G123*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J123" s="23" t="n">
+      <c r="J123" s="27" t="n">
         <v>94.8</v>
       </c>
       <c r="K123" s="10" t="n">
@@ -9528,18 +10258,18 @@
           <t>H</t>
         </is>
       </c>
-      <c r="G124" s="21" t="n">
+      <c r="G124" s="25" t="n">
         <v>64.40000000000001</v>
       </c>
       <c r="H124" s="10">
         <f>G124/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I124" s="22">
+      <c r="I124" s="26">
         <f>G124*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J124" s="23" t="n">
+      <c r="J124" s="27" t="n">
         <v>74.8</v>
       </c>
       <c r="K124" s="10" t="n">
@@ -9583,18 +10313,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G125" s="21" t="n">
+      <c r="G125" s="25" t="n">
         <v>63.6</v>
       </c>
       <c r="H125" s="10">
         <f>G125/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I125" s="22">
+      <c r="I125" s="26">
         <f>G125*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J125" s="23" t="n">
+      <c r="J125" s="27" t="n">
         <v>46.8</v>
       </c>
       <c r="K125" s="10" t="n">
@@ -9638,18 +10368,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G126" s="21" t="n">
+      <c r="G126" s="25" t="n">
         <v>63.2</v>
       </c>
       <c r="H126" s="10">
         <f>G126/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I126" s="22">
+      <c r="I126" s="26">
         <f>G126*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J126" s="23" t="n">
+      <c r="J126" s="27" t="n">
         <v>115.9</v>
       </c>
       <c r="K126" s="10" t="n">
@@ -9693,18 +10423,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G127" s="21" t="n">
+      <c r="G127" s="25" t="n">
         <v>61.4</v>
       </c>
       <c r="H127" s="10">
         <f>G127/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I127" s="22">
+      <c r="I127" s="26">
         <f>G127*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J127" s="23" t="n">
+      <c r="J127" s="27" t="n">
         <v>16.4</v>
       </c>
       <c r="K127" s="10" t="n">
@@ -9744,18 +10474,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G128" s="21" t="n">
+      <c r="G128" s="25" t="n">
         <v>61.3</v>
       </c>
       <c r="H128" s="10">
         <f>G128/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I128" s="22">
+      <c r="I128" s="26">
         <f>G128*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J128" s="23" t="n">
+      <c r="J128" s="27" t="n">
         <v>43.9</v>
       </c>
       <c r="K128" s="10" t="n">
@@ -9795,18 +10525,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G129" s="21" t="n">
+      <c r="G129" s="25" t="n">
         <v>60.7</v>
       </c>
       <c r="H129" s="10">
         <f>G129/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I129" s="22">
+      <c r="I129" s="26">
         <f>G129*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J129" s="23" t="n">
+      <c r="J129" s="27" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="K129" s="10" t="n">
@@ -9846,18 +10576,18 @@
           <t>H</t>
         </is>
       </c>
-      <c r="G130" s="21" t="n">
+      <c r="G130" s="25" t="n">
         <v>57.6</v>
       </c>
       <c r="H130" s="10">
         <f>G130/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I130" s="22">
+      <c r="I130" s="26">
         <f>G130*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J130" s="23" t="n">
+      <c r="J130" s="27" t="n">
         <v>88.3</v>
       </c>
       <c r="K130" s="10" t="n">
@@ -9901,18 +10631,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G131" s="21" t="n">
+      <c r="G131" s="25" t="n">
         <v>57.2</v>
       </c>
       <c r="H131" s="10">
         <f>G131/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I131" s="22">
+      <c r="I131" s="26">
         <f>G131*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J131" s="23" t="n">
+      <c r="J131" s="27" t="n">
         <v>83.3</v>
       </c>
       <c r="K131" s="10" t="n">
@@ -9956,18 +10686,18 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G132" s="21" t="n">
+      <c r="G132" s="25" t="n">
         <v>57.1</v>
       </c>
       <c r="H132" s="10">
         <f>G132/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I132" s="22">
+      <c r="I132" s="26">
         <f>G132*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J132" s="23" t="n">
+      <c r="J132" s="27" t="n">
         <v>81.5</v>
       </c>
       <c r="K132" s="10" t="n">
@@ -10011,18 +10741,18 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G133" s="21" t="n">
+      <c r="G133" s="25" t="n">
         <v>56.9</v>
       </c>
       <c r="H133" s="10">
         <f>G133/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I133" s="22">
+      <c r="I133" s="26">
         <f>G133*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J133" s="23" t="n">
+      <c r="J133" s="27" t="n">
         <v>92.8</v>
       </c>
       <c r="K133" s="10" t="n">
@@ -10066,18 +10796,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G134" s="21" t="n">
+      <c r="G134" s="25" t="n">
         <v>52.6</v>
       </c>
       <c r="H134" s="10">
         <f>G134/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I134" s="22">
+      <c r="I134" s="26">
         <f>G134*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J134" s="23" t="n">
+      <c r="J134" s="27" t="n">
         <v>28.9</v>
       </c>
       <c r="K134" s="10" t="n">
@@ -10121,18 +10851,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G135" s="21" t="n">
+      <c r="G135" s="25" t="n">
         <v>52.3</v>
       </c>
       <c r="H135" s="10">
         <f>G135/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I135" s="22">
+      <c r="I135" s="26">
         <f>G135*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J135" s="23" t="n">
+      <c r="J135" s="27" t="n">
         <v>76.40000000000001</v>
       </c>
       <c r="K135" s="10" t="n">
@@ -10172,18 +10902,18 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G136" s="21" t="n">
+      <c r="G136" s="25" t="n">
         <v>52.2</v>
       </c>
       <c r="H136" s="10">
         <f>G136/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I136" s="22">
+      <c r="I136" s="26">
         <f>G136*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J136" s="23" t="n">
+      <c r="J136" s="27" t="n">
         <v>138.1</v>
       </c>
       <c r="K136" s="10" t="n">
@@ -10227,18 +10957,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G137" s="21" t="n">
+      <c r="G137" s="25" t="n">
         <v>52</v>
       </c>
       <c r="H137" s="10">
         <f>G137/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I137" s="22">
+      <c r="I137" s="26">
         <f>G137*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J137" s="23" t="n">
+      <c r="J137" s="27" t="n">
         <v>69.90000000000001</v>
       </c>
       <c r="K137" s="10" t="n">
@@ -10282,18 +11012,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G138" s="21" t="n">
+      <c r="G138" s="25" t="n">
         <v>51.5</v>
       </c>
       <c r="H138" s="10">
         <f>G138/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I138" s="22">
+      <c r="I138" s="26">
         <f>G138*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J138" s="23" t="n">
+      <c r="J138" s="27" t="n">
         <v>46.4</v>
       </c>
       <c r="K138" s="10" t="n">
@@ -10337,18 +11067,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G139" s="21" t="n">
+      <c r="G139" s="25" t="n">
         <v>51.3</v>
       </c>
       <c r="H139" s="10">
         <f>G139/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I139" s="22">
+      <c r="I139" s="26">
         <f>G139*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J139" s="23" t="n">
+      <c r="J139" s="27" t="n">
         <v>197</v>
       </c>
       <c r="K139" s="10" t="n">
@@ -10392,18 +11122,18 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G140" s="21" t="n">
+      <c r="G140" s="25" t="n">
         <v>51</v>
       </c>
       <c r="H140" s="10">
         <f>G140/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I140" s="22">
+      <c r="I140" s="26">
         <f>G140*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J140" s="23" t="n">
+      <c r="J140" s="27" t="n">
         <v>87.7</v>
       </c>
       <c r="K140" s="10" t="n">
@@ -10447,18 +11177,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G141" s="21" t="n">
+      <c r="G141" s="25" t="n">
         <v>50.4</v>
       </c>
       <c r="H141" s="10">
         <f>G141/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I141" s="22">
+      <c r="I141" s="26">
         <f>G141*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J141" s="23" t="n">
+      <c r="J141" s="27" t="n">
         <v>61.1</v>
       </c>
       <c r="K141" s="10" t="n">
@@ -10502,18 +11232,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G142" s="21" t="n">
+      <c r="G142" s="25" t="n">
         <v>50</v>
       </c>
       <c r="H142" s="10">
         <f>G142/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I142" s="22">
+      <c r="I142" s="26">
         <f>G142*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J142" s="23" t="n">
+      <c r="J142" s="27" t="n">
         <v>35.4</v>
       </c>
       <c r="K142" s="10" t="n">
@@ -10557,18 +11287,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G143" s="21" t="n">
+      <c r="G143" s="25" t="n">
         <v>49.3</v>
       </c>
       <c r="H143" s="10">
         <f>G143/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I143" s="22">
+      <c r="I143" s="26">
         <f>G143*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J143" s="23" t="n">
+      <c r="J143" s="27" t="n">
         <v>37.8</v>
       </c>
       <c r="K143" s="10" t="n">
@@ -10608,18 +11338,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G144" s="21" t="n">
+      <c r="G144" s="25" t="n">
         <v>48.7</v>
       </c>
       <c r="H144" s="10">
         <f>G144/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I144" s="22">
+      <c r="I144" s="26">
         <f>G144*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J144" s="23" t="n">
+      <c r="J144" s="27" t="n">
         <v>33.8</v>
       </c>
       <c r="K144" s="10" t="n">
@@ -10659,18 +11389,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G145" s="21" t="n">
+      <c r="G145" s="25" t="n">
         <v>47.8</v>
       </c>
       <c r="H145" s="10">
         <f>G145/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I145" s="22">
+      <c r="I145" s="26">
         <f>G145*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J145" s="23" t="n">
+      <c r="J145" s="27" t="n">
         <v>31.1</v>
       </c>
       <c r="K145" s="10" t="n">
@@ -10714,18 +11444,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G146" s="21" t="n">
+      <c r="G146" s="25" t="n">
         <v>47.4</v>
       </c>
       <c r="H146" s="10">
         <f>G146/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I146" s="22">
+      <c r="I146" s="26">
         <f>G146*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J146" s="23" t="n">
+      <c r="J146" s="27" t="n">
         <v>84.7</v>
       </c>
       <c r="K146" s="10" t="n">
@@ -10769,18 +11499,18 @@
           <t>H</t>
         </is>
       </c>
-      <c r="G147" s="21" t="n">
+      <c r="G147" s="25" t="n">
         <v>47.4</v>
       </c>
       <c r="H147" s="10">
         <f>G147/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I147" s="22">
+      <c r="I147" s="26">
         <f>G147*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J147" s="23" t="n">
+      <c r="J147" s="27" t="n">
         <v>60.3</v>
       </c>
       <c r="K147" s="10" t="n">
@@ -10824,18 +11554,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G148" s="21" t="n">
+      <c r="G148" s="25" t="n">
         <v>46.9</v>
       </c>
       <c r="H148" s="10">
         <f>G148/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I148" s="22">
+      <c r="I148" s="26">
         <f>G148*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J148" s="23" t="n">
+      <c r="J148" s="27" t="n">
         <v>98.3</v>
       </c>
       <c r="K148" s="10" t="n">
@@ -10879,18 +11609,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G149" s="21" t="n">
+      <c r="G149" s="25" t="n">
         <v>45.6</v>
       </c>
       <c r="H149" s="10">
         <f>G149/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I149" s="22">
+      <c r="I149" s="26">
         <f>G149*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J149" s="23" t="n">
+      <c r="J149" s="27" t="n">
         <v>46.5</v>
       </c>
       <c r="K149" s="10" t="n">
@@ -10934,18 +11664,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G150" s="21" t="n">
+      <c r="G150" s="25" t="n">
         <v>44.6</v>
       </c>
       <c r="H150" s="10">
         <f>G150/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I150" s="22">
+      <c r="I150" s="26">
         <f>G150*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J150" s="23" t="n">
+      <c r="J150" s="27" t="n">
         <v>169.2</v>
       </c>
       <c r="K150" s="10" t="n">
@@ -10989,18 +11719,18 @@
           <t>H</t>
         </is>
       </c>
-      <c r="G151" s="21" t="n">
+      <c r="G151" s="25" t="n">
         <v>44.2</v>
       </c>
       <c r="H151" s="10">
         <f>G151/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I151" s="22">
+      <c r="I151" s="26">
         <f>G151*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J151" s="23" t="n">
+      <c r="J151" s="27" t="n">
         <v>26.1</v>
       </c>
       <c r="K151" s="10" t="n">
@@ -11044,18 +11774,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G152" s="21" t="n">
+      <c r="G152" s="25" t="n">
         <v>43.7</v>
       </c>
       <c r="H152" s="10">
         <f>G152/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I152" s="22">
+      <c r="I152" s="26">
         <f>G152*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J152" s="23" t="n">
+      <c r="J152" s="27" t="n">
         <v>25</v>
       </c>
       <c r="K152" s="10" t="n">
@@ -11095,18 +11825,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G153" s="21" t="n">
+      <c r="G153" s="25" t="n">
         <v>42.1</v>
       </c>
       <c r="H153" s="10">
         <f>G153/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I153" s="22">
+      <c r="I153" s="26">
         <f>G153*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J153" s="23" t="n">
+      <c r="J153" s="27" t="n">
         <v>33.5</v>
       </c>
       <c r="K153" s="10" t="n">
@@ -11150,18 +11880,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G154" s="21" t="n">
+      <c r="G154" s="25" t="n">
         <v>42</v>
       </c>
       <c r="H154" s="10">
         <f>G154/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I154" s="22">
+      <c r="I154" s="26">
         <f>G154*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J154" s="23" t="n">
+      <c r="J154" s="27" t="n">
         <v>48.5</v>
       </c>
       <c r="K154" s="10" t="n">
@@ -11201,18 +11931,18 @@
           <t>H</t>
         </is>
       </c>
-      <c r="G155" s="21" t="n">
+      <c r="G155" s="25" t="n">
         <v>40.9</v>
       </c>
       <c r="H155" s="10">
         <f>G155/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I155" s="22">
+      <c r="I155" s="26">
         <f>G155*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J155" s="23" t="n">
+      <c r="J155" s="27" t="n">
         <v>23.5</v>
       </c>
       <c r="K155" s="10" t="n">
@@ -11256,18 +11986,18 @@
           <t>H</t>
         </is>
       </c>
-      <c r="G156" s="21" t="n">
+      <c r="G156" s="25" t="n">
         <v>40.9</v>
       </c>
       <c r="H156" s="10">
         <f>G156/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I156" s="22">
+      <c r="I156" s="26">
         <f>G156*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J156" s="23" t="n">
+      <c r="J156" s="27" t="n">
         <v>42.8</v>
       </c>
       <c r="K156" s="10" t="n">
@@ -11311,18 +12041,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G157" s="21" t="n">
+      <c r="G157" s="25" t="n">
         <v>40.3</v>
       </c>
       <c r="H157" s="10">
         <f>G157/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I157" s="22">
+      <c r="I157" s="26">
         <f>G157*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J157" s="23" t="n">
+      <c r="J157" s="27" t="n">
         <v>107.3</v>
       </c>
       <c r="K157" s="10" t="n">
@@ -11366,18 +12096,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G158" s="21" t="n">
+      <c r="G158" s="25" t="n">
         <v>38.5</v>
       </c>
       <c r="H158" s="10">
         <f>G158/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I158" s="22">
+      <c r="I158" s="26">
         <f>G158*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J158" s="23" t="n">
+      <c r="J158" s="27" t="n">
         <v>65.59999999999999</v>
       </c>
       <c r="K158" s="10" t="n">
@@ -11421,18 +12151,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G159" s="21" t="n">
+      <c r="G159" s="25" t="n">
         <v>37.9</v>
       </c>
       <c r="H159" s="10">
         <f>G159/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I159" s="22">
+      <c r="I159" s="26">
         <f>G159*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J159" s="23" t="n">
+      <c r="J159" s="27" t="n">
         <v>26</v>
       </c>
       <c r="K159" s="10" t="n">
@@ -11476,18 +12206,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G160" s="21" t="n">
+      <c r="G160" s="25" t="n">
         <v>37.6</v>
       </c>
       <c r="H160" s="10">
         <f>G160/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I160" s="22">
+      <c r="I160" s="26">
         <f>G160*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J160" s="23" t="n">
+      <c r="J160" s="27" t="n">
         <v>44.4</v>
       </c>
       <c r="K160" s="10" t="n">
@@ -11531,18 +12261,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G161" s="21" t="n">
+      <c r="G161" s="25" t="n">
         <v>37.4</v>
       </c>
       <c r="H161" s="10">
         <f>G161/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I161" s="22">
+      <c r="I161" s="26">
         <f>G161*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J161" s="23" t="n">
+      <c r="J161" s="27" t="n">
         <v>78.59999999999999</v>
       </c>
       <c r="K161" s="10" t="n">
@@ -11586,18 +12316,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G162" s="21" t="n">
+      <c r="G162" s="25" t="n">
         <v>36.9</v>
       </c>
       <c r="H162" s="10">
         <f>G162/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I162" s="22">
+      <c r="I162" s="26">
         <f>G162*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J162" s="23" t="n">
+      <c r="J162" s="27" t="n">
         <v>50.4</v>
       </c>
       <c r="K162" s="10" t="n">
@@ -11641,18 +12371,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G163" s="21" t="n">
+      <c r="G163" s="25" t="n">
         <v>36.9</v>
       </c>
       <c r="H163" s="10">
         <f>G163/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I163" s="22">
+      <c r="I163" s="26">
         <f>G163*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J163" s="23" t="n">
+      <c r="J163" s="27" t="n">
         <v>38.7</v>
       </c>
       <c r="K163" s="10" t="n">
@@ -11696,18 +12426,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G164" s="21" t="n">
+      <c r="G164" s="25" t="n">
         <v>36.7</v>
       </c>
       <c r="H164" s="10">
         <f>G164/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I164" s="22">
+      <c r="I164" s="26">
         <f>G164*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J164" s="23" t="n">
+      <c r="J164" s="27" t="n">
         <v>16.3</v>
       </c>
       <c r="K164" s="10" t="n">
@@ -11747,18 +12477,18 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G165" s="21" t="n">
+      <c r="G165" s="25" t="n">
         <v>36.6</v>
       </c>
       <c r="H165" s="10">
         <f>G165/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I165" s="22">
+      <c r="I165" s="26">
         <f>G165*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J165" s="23" t="n">
+      <c r="J165" s="27" t="n">
         <v>64.90000000000001</v>
       </c>
       <c r="K165" s="10" t="n">
@@ -11802,18 +12532,18 @@
           <t>H</t>
         </is>
       </c>
-      <c r="G166" s="21" t="n">
+      <c r="G166" s="25" t="n">
         <v>35.6</v>
       </c>
       <c r="H166" s="10">
         <f>G166/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I166" s="22">
+      <c r="I166" s="26">
         <f>G166*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J166" s="23" t="n">
+      <c r="J166" s="27" t="n">
         <v>98</v>
       </c>
       <c r="K166" s="10" t="n">
@@ -11857,18 +12587,18 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G167" s="21" t="n">
+      <c r="G167" s="25" t="n">
         <v>34.9</v>
       </c>
       <c r="H167" s="10">
         <f>G167/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I167" s="22">
+      <c r="I167" s="26">
         <f>G167*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J167" s="23" t="n">
+      <c r="J167" s="27" t="n">
         <v>82.40000000000001</v>
       </c>
       <c r="K167" s="10" t="n">
@@ -11912,18 +12642,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G168" s="21" t="n">
+      <c r="G168" s="25" t="n">
         <v>34.2</v>
       </c>
       <c r="H168" s="10">
         <f>G168/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I168" s="22">
+      <c r="I168" s="26">
         <f>G168*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J168" s="23" t="n">
+      <c r="J168" s="27" t="n">
         <v>51.5</v>
       </c>
       <c r="K168" s="10" t="n">
@@ -11967,18 +12697,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G169" s="21" t="n">
+      <c r="G169" s="25" t="n">
         <v>34.1</v>
       </c>
       <c r="H169" s="10">
         <f>G169/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I169" s="22">
+      <c r="I169" s="26">
         <f>G169*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J169" s="23" t="n">
+      <c r="J169" s="27" t="n">
         <v>34.9</v>
       </c>
       <c r="K169" s="10" t="n">
@@ -12022,18 +12752,18 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G170" s="21" t="n">
+      <c r="G170" s="25" t="n">
         <v>34</v>
       </c>
       <c r="H170" s="10">
         <f>G170/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I170" s="22">
+      <c r="I170" s="26">
         <f>G170*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J170" s="23" t="n">
+      <c r="J170" s="27" t="n">
         <v>54</v>
       </c>
       <c r="K170" s="10" t="n">
@@ -12077,18 +12807,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G171" s="21" t="n">
+      <c r="G171" s="25" t="n">
         <v>34</v>
       </c>
       <c r="H171" s="10">
         <f>G171/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I171" s="22">
+      <c r="I171" s="26">
         <f>G171*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J171" s="23" t="n">
+      <c r="J171" s="27" t="n">
         <v>77.59999999999999</v>
       </c>
       <c r="K171" s="10" t="n">
@@ -12132,18 +12862,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G172" s="21" t="n">
+      <c r="G172" s="25" t="n">
         <v>33.8</v>
       </c>
       <c r="H172" s="10">
         <f>G172/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I172" s="22">
+      <c r="I172" s="26">
         <f>G172*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J172" s="23" t="n">
+      <c r="J172" s="27" t="n">
         <v>65.40000000000001</v>
       </c>
       <c r="K172" s="10" t="n">
@@ -12187,18 +12917,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G173" s="21" t="n">
+      <c r="G173" s="25" t="n">
         <v>33.3</v>
       </c>
       <c r="H173" s="10">
         <f>G173/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I173" s="22">
+      <c r="I173" s="26">
         <f>G173*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J173" s="23" t="n">
+      <c r="J173" s="27" t="n">
         <v>7.1</v>
       </c>
       <c r="K173" s="10" t="n">
@@ -12238,18 +12968,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G174" s="21" t="n">
+      <c r="G174" s="25" t="n">
         <v>33.2</v>
       </c>
       <c r="H174" s="10">
         <f>G174/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I174" s="22">
+      <c r="I174" s="26">
         <f>G174*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J174" s="23" t="n">
+      <c r="J174" s="27" t="n">
         <v>54.6</v>
       </c>
       <c r="K174" s="10" t="n">
@@ -12293,18 +13023,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G175" s="21" t="n">
+      <c r="G175" s="25" t="n">
         <v>31.8</v>
       </c>
       <c r="H175" s="10">
         <f>G175/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I175" s="22">
+      <c r="I175" s="26">
         <f>G175*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J175" s="23" t="n">
+      <c r="J175" s="27" t="n">
         <v>69.7</v>
       </c>
       <c r="K175" s="10" t="n">
@@ -12348,18 +13078,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G176" s="21" t="n">
+      <c r="G176" s="25" t="n">
         <v>31.8</v>
       </c>
       <c r="H176" s="10">
         <f>G176/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I176" s="22">
+      <c r="I176" s="26">
         <f>G176*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J176" s="23" t="n">
+      <c r="J176" s="27" t="n">
         <v>45.1</v>
       </c>
       <c r="K176" s="10" t="n">
@@ -12399,18 +13129,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G177" s="21" t="n">
+      <c r="G177" s="25" t="n">
         <v>31.5</v>
       </c>
       <c r="H177" s="10">
         <f>G177/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I177" s="22">
+      <c r="I177" s="26">
         <f>G177*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J177" s="23" t="n">
+      <c r="J177" s="27" t="n">
         <v>29.3</v>
       </c>
       <c r="K177" s="10" t="n">
@@ -12454,18 +13184,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G178" s="21" t="n">
+      <c r="G178" s="25" t="n">
         <v>29.9</v>
       </c>
       <c r="H178" s="10">
         <f>G178/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I178" s="22">
+      <c r="I178" s="26">
         <f>G178*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J178" s="23" t="n">
+      <c r="J178" s="27" t="n">
         <v>11.8</v>
       </c>
       <c r="K178" s="10" t="n">
@@ -12505,18 +13235,18 @@
           <t>H</t>
         </is>
       </c>
-      <c r="G179" s="21" t="n">
+      <c r="G179" s="25" t="n">
         <v>29.7</v>
       </c>
       <c r="H179" s="10">
         <f>G179/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I179" s="22">
+      <c r="I179" s="26">
         <f>G179*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J179" s="23" t="n">
+      <c r="J179" s="27" t="n">
         <v>27.4</v>
       </c>
       <c r="K179" s="10" t="n">
@@ -12560,18 +13290,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G180" s="21" t="n">
+      <c r="G180" s="25" t="n">
         <v>28.3</v>
       </c>
       <c r="H180" s="10">
         <f>G180/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I180" s="22">
+      <c r="I180" s="26">
         <f>G180*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J180" s="23" t="n">
+      <c r="J180" s="27" t="n">
         <v>4.3</v>
       </c>
       <c r="K180" s="10" t="n">
@@ -12611,18 +13341,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G181" s="21" t="n">
+      <c r="G181" s="25" t="n">
         <v>28.1</v>
       </c>
       <c r="H181" s="10">
         <f>G181/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I181" s="22">
+      <c r="I181" s="26">
         <f>G181*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J181" s="23" t="n">
+      <c r="J181" s="27" t="n">
         <v>11.8</v>
       </c>
       <c r="K181" s="10" t="n">
@@ -12662,18 +13392,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G182" s="21" t="n">
+      <c r="G182" s="25" t="n">
         <v>28.1</v>
       </c>
       <c r="H182" s="10">
         <f>G182/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I182" s="22">
+      <c r="I182" s="26">
         <f>G182*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J182" s="23" t="n">
+      <c r="J182" s="27" t="n">
         <v>13.1</v>
       </c>
       <c r="K182" s="10" t="n">
@@ -12713,18 +13443,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G183" s="21" t="n">
+      <c r="G183" s="25" t="n">
         <v>28</v>
       </c>
       <c r="H183" s="10">
         <f>G183/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I183" s="22">
+      <c r="I183" s="26">
         <f>G183*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J183" s="23" t="n">
+      <c r="J183" s="27" t="n">
         <v>26.3</v>
       </c>
       <c r="K183" s="10" t="n">
@@ -12764,18 +13494,18 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G184" s="21" t="n">
+      <c r="G184" s="25" t="n">
         <v>27.5</v>
       </c>
       <c r="H184" s="10">
         <f>G184/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I184" s="22">
+      <c r="I184" s="26">
         <f>G184*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J184" s="23" t="n">
+      <c r="J184" s="27" t="n">
         <v>87.90000000000001</v>
       </c>
       <c r="K184" s="10" t="n">
@@ -12819,18 +13549,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G185" s="21" t="n">
+      <c r="G185" s="25" t="n">
         <v>27.1</v>
       </c>
       <c r="H185" s="10">
         <f>G185/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I185" s="22">
+      <c r="I185" s="26">
         <f>G185*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J185" s="23" t="n">
+      <c r="J185" s="27" t="n">
         <v>54.3</v>
       </c>
       <c r="K185" s="10" t="n">
@@ -12874,18 +13604,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G186" s="21" t="n">
+      <c r="G186" s="25" t="n">
         <v>25.8</v>
       </c>
       <c r="H186" s="10">
         <f>G186/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I186" s="22">
+      <c r="I186" s="26">
         <f>G186*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J186" s="23" t="n">
+      <c r="J186" s="27" t="n">
         <v>38.8</v>
       </c>
       <c r="K186" s="10" t="n">
@@ -12929,18 +13659,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G187" s="21" t="n">
+      <c r="G187" s="25" t="n">
         <v>25.3</v>
       </c>
       <c r="H187" s="10">
         <f>G187/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I187" s="22">
+      <c r="I187" s="26">
         <f>G187*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J187" s="23" t="n">
+      <c r="J187" s="27" t="n">
         <v>66.59999999999999</v>
       </c>
       <c r="K187" s="10" t="n">
@@ -12980,18 +13710,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G188" s="21" t="n">
+      <c r="G188" s="25" t="n">
         <v>24.1</v>
       </c>
       <c r="H188" s="10">
         <f>G188/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I188" s="22">
+      <c r="I188" s="26">
         <f>G188*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J188" s="23" t="n">
+      <c r="J188" s="27" t="n">
         <v>23</v>
       </c>
       <c r="K188" s="10" t="n">
@@ -13031,18 +13761,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G189" s="21" t="n">
+      <c r="G189" s="25" t="n">
         <v>23.5</v>
       </c>
       <c r="H189" s="10">
         <f>G189/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I189" s="22">
+      <c r="I189" s="26">
         <f>G189*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J189" s="23" t="n">
+      <c r="J189" s="27" t="n">
         <v>27.6</v>
       </c>
       <c r="K189" s="10" t="n">
@@ -13086,18 +13816,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G190" s="21" t="n">
+      <c r="G190" s="25" t="n">
         <v>23</v>
       </c>
       <c r="H190" s="10">
         <f>G190/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I190" s="22">
+      <c r="I190" s="26">
         <f>G190*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J190" s="23" t="n">
+      <c r="J190" s="27" t="n">
         <v>24.4</v>
       </c>
       <c r="K190" s="10" t="n">
@@ -13137,18 +13867,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G191" s="21" t="n">
+      <c r="G191" s="25" t="n">
         <v>22.6</v>
       </c>
       <c r="H191" s="10">
         <f>G191/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I191" s="22">
+      <c r="I191" s="26">
         <f>G191*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J191" s="23" t="n">
+      <c r="J191" s="27" t="n">
         <v>27</v>
       </c>
       <c r="K191" s="10" t="n">
@@ -13192,18 +13922,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G192" s="21" t="n">
+      <c r="G192" s="25" t="n">
         <v>22.1</v>
       </c>
       <c r="H192" s="10">
         <f>G192/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I192" s="22">
+      <c r="I192" s="26">
         <f>G192*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J192" s="23" t="n">
+      <c r="J192" s="27" t="n">
         <v>37.9</v>
       </c>
       <c r="K192" s="10" t="n">
@@ -13247,18 +13977,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G193" s="21" t="n">
+      <c r="G193" s="25" t="n">
         <v>22</v>
       </c>
       <c r="H193" s="10">
         <f>G193/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I193" s="22">
+      <c r="I193" s="26">
         <f>G193*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J193" s="23" t="n">
+      <c r="J193" s="27" t="n">
         <v>54.9</v>
       </c>
       <c r="K193" s="10" t="n">
@@ -13298,18 +14028,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G194" s="21" t="n">
+      <c r="G194" s="25" t="n">
         <v>21.7</v>
       </c>
       <c r="H194" s="10">
         <f>G194/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I194" s="22">
+      <c r="I194" s="26">
         <f>G194*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J194" s="23" t="n">
+      <c r="J194" s="27" t="n">
         <v>15</v>
       </c>
       <c r="K194" s="10" t="n">
@@ -13349,18 +14079,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G195" s="21" t="n">
+      <c r="G195" s="25" t="n">
         <v>21.1</v>
       </c>
       <c r="H195" s="10">
         <f>G195/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I195" s="22">
+      <c r="I195" s="26">
         <f>G195*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J195" s="23" t="n">
+      <c r="J195" s="27" t="n">
         <v>38.2</v>
       </c>
       <c r="K195" s="10" t="n">
@@ -13404,18 +14134,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G196" s="21" t="n">
+      <c r="G196" s="25" t="n">
         <v>20.5</v>
       </c>
       <c r="H196" s="10">
         <f>G196/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I196" s="22">
+      <c r="I196" s="26">
         <f>G196*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J196" s="23" t="n">
+      <c r="J196" s="27" t="n">
         <v>44.8</v>
       </c>
       <c r="K196" s="10" t="n">
@@ -13459,18 +14189,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G197" s="21" t="n">
+      <c r="G197" s="25" t="n">
         <v>20.4</v>
       </c>
       <c r="H197" s="10">
         <f>G197/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I197" s="22">
+      <c r="I197" s="26">
         <f>G197*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J197" s="23" t="n">
+      <c r="J197" s="27" t="n">
         <v>14.9</v>
       </c>
       <c r="K197" s="10" t="n">
@@ -13510,18 +14240,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G198" s="21" t="n">
+      <c r="G198" s="25" t="n">
         <v>19.9</v>
       </c>
       <c r="H198" s="10">
         <f>G198/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I198" s="22">
+      <c r="I198" s="26">
         <f>G198*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J198" s="23" t="n">
+      <c r="J198" s="27" t="n">
         <v>191.4</v>
       </c>
       <c r="K198" s="10" t="n">
@@ -13565,18 +14295,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G199" s="21" t="n">
+      <c r="G199" s="25" t="n">
         <v>19.8</v>
       </c>
       <c r="H199" s="10">
         <f>G199/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I199" s="22">
+      <c r="I199" s="26">
         <f>G199*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J199" s="23" t="n">
+      <c r="J199" s="27" t="n">
         <v>24.8</v>
       </c>
       <c r="K199" s="10" t="n">
@@ -13616,18 +14346,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G200" s="21" t="n">
+      <c r="G200" s="25" t="n">
         <v>18.8</v>
       </c>
       <c r="H200" s="10">
         <f>G200/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I200" s="22">
+      <c r="I200" s="26">
         <f>G200*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J200" s="23" t="n">
+      <c r="J200" s="27" t="n">
         <v>36</v>
       </c>
       <c r="K200" s="10" t="n">
@@ -13667,18 +14397,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G201" s="21" t="n">
+      <c r="G201" s="25" t="n">
         <v>18.7</v>
       </c>
       <c r="H201" s="10">
         <f>G201/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I201" s="22">
+      <c r="I201" s="26">
         <f>G201*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J201" s="23" t="n">
+      <c r="J201" s="27" t="n">
         <v>36.8</v>
       </c>
       <c r="K201" s="10" t="n">
@@ -13718,18 +14448,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G202" s="21" t="n">
+      <c r="G202" s="25" t="n">
         <v>18.1</v>
       </c>
       <c r="H202" s="10">
         <f>G202/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I202" s="22">
+      <c r="I202" s="26">
         <f>G202*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J202" s="23" t="n">
+      <c r="J202" s="27" t="n">
         <v>8</v>
       </c>
       <c r="K202" s="10" t="n">
@@ -13769,18 +14499,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G203" s="21" t="n">
+      <c r="G203" s="25" t="n">
         <v>17.4</v>
       </c>
       <c r="H203" s="10">
         <f>G203/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I203" s="22">
+      <c r="I203" s="26">
         <f>G203*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J203" s="23" t="n">
+      <c r="J203" s="27" t="n">
         <v>31</v>
       </c>
       <c r="K203" s="10" t="n">
@@ -13820,18 +14550,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G204" s="21" t="n">
+      <c r="G204" s="25" t="n">
         <v>16.6</v>
       </c>
       <c r="H204" s="10">
         <f>G204/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I204" s="22">
+      <c r="I204" s="26">
         <f>G204*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J204" s="23" t="n">
+      <c r="J204" s="27" t="n">
         <v>22.1</v>
       </c>
       <c r="K204" s="10" t="n">
@@ -13875,18 +14605,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G205" s="21" t="n">
+      <c r="G205" s="25" t="n">
         <v>15.8</v>
       </c>
       <c r="H205" s="10">
         <f>G205/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I205" s="22">
+      <c r="I205" s="26">
         <f>G205*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J205" s="23" t="n">
+      <c r="J205" s="27" t="n">
         <v>12.7</v>
       </c>
       <c r="K205" s="10" t="n">
@@ -13926,18 +14656,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G206" s="21" t="n">
+      <c r="G206" s="25" t="n">
         <v>15.5</v>
       </c>
       <c r="H206" s="10">
         <f>G206/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I206" s="22">
+      <c r="I206" s="26">
         <f>G206*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J206" s="23" t="n">
+      <c r="J206" s="27" t="n">
         <v>3.5</v>
       </c>
       <c r="K206" s="10" t="n">
@@ -13977,18 +14707,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G207" s="21" t="n">
+      <c r="G207" s="25" t="n">
         <v>15.5</v>
       </c>
       <c r="H207" s="10">
         <f>G207/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I207" s="22">
+      <c r="I207" s="26">
         <f>G207*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J207" s="23" t="n">
+      <c r="J207" s="27" t="n">
         <v>20.5</v>
       </c>
       <c r="K207" s="10" t="n">
@@ -14032,18 +14762,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G208" s="21" t="n">
+      <c r="G208" s="25" t="n">
         <v>15.3</v>
       </c>
       <c r="H208" s="10">
         <f>G208/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I208" s="22">
+      <c r="I208" s="26">
         <f>G208*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J208" s="23" t="n">
+      <c r="J208" s="27" t="n">
         <v>18</v>
       </c>
       <c r="K208" s="10" t="n">
@@ -14083,18 +14813,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G209" s="21" t="n">
+      <c r="G209" s="25" t="n">
         <v>15</v>
       </c>
       <c r="H209" s="10">
         <f>G209/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I209" s="22">
+      <c r="I209" s="26">
         <f>G209*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J209" s="23" t="n">
+      <c r="J209" s="27" t="n">
         <v>6.1</v>
       </c>
       <c r="K209" s="10" t="n">
@@ -14134,18 +14864,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G210" s="21" t="n">
+      <c r="G210" s="25" t="n">
         <v>14.7</v>
       </c>
       <c r="H210" s="10">
         <f>G210/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I210" s="22">
+      <c r="I210" s="26">
         <f>G210*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J210" s="23" t="n">
+      <c r="J210" s="27" t="n">
         <v>16.5</v>
       </c>
       <c r="K210" s="10" t="n">
@@ -14185,18 +14915,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G211" s="21" t="n">
+      <c r="G211" s="25" t="n">
         <v>14.5</v>
       </c>
       <c r="H211" s="10">
         <f>G211/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I211" s="22">
+      <c r="I211" s="26">
         <f>G211*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J211" s="23" t="n">
+      <c r="J211" s="27" t="n">
         <v>16.4</v>
       </c>
       <c r="K211" s="10" t="n">
@@ -14236,18 +14966,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G212" s="21" t="n">
+      <c r="G212" s="25" t="n">
         <v>14.4</v>
       </c>
       <c r="H212" s="10">
         <f>G212/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I212" s="22">
+      <c r="I212" s="26">
         <f>G212*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J212" s="23" t="n">
+      <c r="J212" s="27" t="n">
         <v>32.2</v>
       </c>
       <c r="K212" s="10" t="n">
@@ -14291,18 +15021,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G213" s="21" t="n">
+      <c r="G213" s="25" t="n">
         <v>14.1</v>
       </c>
       <c r="H213" s="10">
         <f>G213/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I213" s="22">
+      <c r="I213" s="26">
         <f>G213*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J213" s="23" t="n">
+      <c r="J213" s="27" t="n">
         <v>33.1</v>
       </c>
       <c r="K213" s="10" t="n">
@@ -14342,18 +15072,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G214" s="21" t="n">
+      <c r="G214" s="25" t="n">
         <v>13</v>
       </c>
       <c r="H214" s="10">
         <f>G214/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I214" s="22">
+      <c r="I214" s="26">
         <f>G214*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J214" s="23" t="n">
+      <c r="J214" s="27" t="n">
         <v>42</v>
       </c>
       <c r="K214" s="10" t="n">
@@ -14397,18 +15127,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G215" s="21" t="n">
+      <c r="G215" s="25" t="n">
         <v>12.9</v>
       </c>
       <c r="H215" s="10">
         <f>G215/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I215" s="22">
+      <c r="I215" s="26">
         <f>G215*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J215" s="23" t="n">
+      <c r="J215" s="27" t="n">
         <v>22.8</v>
       </c>
       <c r="K215" s="10" t="n">
@@ -14452,18 +15182,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G216" s="21" t="n">
+      <c r="G216" s="25" t="n">
         <v>12.6</v>
       </c>
       <c r="H216" s="10">
         <f>G216/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I216" s="22">
+      <c r="I216" s="26">
         <f>G216*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J216" s="23" t="n">
+      <c r="J216" s="27" t="n">
         <v>21.6</v>
       </c>
       <c r="K216" s="10" t="n">
@@ -14503,18 +15233,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G217" s="21" t="n">
+      <c r="G217" s="25" t="n">
         <v>12</v>
       </c>
       <c r="H217" s="10">
         <f>G217/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I217" s="22">
+      <c r="I217" s="26">
         <f>G217*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J217" s="23" t="n">
+      <c r="J217" s="27" t="n">
         <v>14.8</v>
       </c>
       <c r="K217" s="10" t="n">
@@ -14554,18 +15284,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G218" s="21" t="n">
+      <c r="G218" s="25" t="n">
         <v>10.7</v>
       </c>
       <c r="H218" s="10">
         <f>G218/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I218" s="22">
+      <c r="I218" s="26">
         <f>G218*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J218" s="23" t="n">
+      <c r="J218" s="27" t="n">
         <v>24.8</v>
       </c>
       <c r="K218" s="10" t="n">
@@ -14609,18 +15339,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G219" s="21" t="n">
+      <c r="G219" s="25" t="n">
         <v>10.5</v>
       </c>
       <c r="H219" s="10">
         <f>G219/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I219" s="22">
+      <c r="I219" s="26">
         <f>G219*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J219" s="23" t="n">
+      <c r="J219" s="27" t="n">
         <v>2.5</v>
       </c>
       <c r="K219" s="10" t="n">
@@ -14660,18 +15390,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G220" s="21" t="n">
+      <c r="G220" s="25" t="n">
         <v>10.5</v>
       </c>
       <c r="H220" s="10">
         <f>G220/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I220" s="22">
+      <c r="I220" s="26">
         <f>G220*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J220" s="23" t="n">
+      <c r="J220" s="27" t="n">
         <v>54.1</v>
       </c>
       <c r="K220" s="10" t="n">
@@ -14715,18 +15445,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G221" s="21" t="n">
+      <c r="G221" s="25" t="n">
         <v>10</v>
       </c>
       <c r="H221" s="10">
         <f>G221/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I221" s="22">
+      <c r="I221" s="26">
         <f>G221*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J221" s="23" t="n">
+      <c r="J221" s="27" t="n">
         <v>18.5</v>
       </c>
       <c r="K221" s="10" t="n">
@@ -14766,18 +15496,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G222" s="21" t="n">
+      <c r="G222" s="25" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="H222" s="10">
         <f>G222/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I222" s="22">
+      <c r="I222" s="26">
         <f>G222*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J222" s="23" t="n">
+      <c r="J222" s="27" t="n">
         <v>29.1</v>
       </c>
       <c r="K222" s="10" t="n">
@@ -14821,18 +15551,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G223" s="21" t="n">
+      <c r="G223" s="25" t="n">
         <v>9.5</v>
       </c>
       <c r="H223" s="10">
         <f>G223/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I223" s="22">
+      <c r="I223" s="26">
         <f>G223*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J223" s="23" t="n">
+      <c r="J223" s="27" t="n">
         <v>5</v>
       </c>
       <c r="K223" s="10" t="n">
@@ -14872,18 +15602,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G224" s="21" t="n">
+      <c r="G224" s="25" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="H224" s="10">
         <f>G224/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I224" s="22">
+      <c r="I224" s="26">
         <f>G224*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J224" s="23" t="n">
+      <c r="J224" s="27" t="n">
         <v>8.5</v>
       </c>
       <c r="K224" s="10" t="n">
@@ -14923,18 +15653,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G225" s="21" t="n">
+      <c r="G225" s="25" t="n">
         <v>8.1</v>
       </c>
       <c r="H225" s="10">
         <f>G225/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I225" s="22">
+      <c r="I225" s="26">
         <f>G225*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J225" s="23" t="n">
+      <c r="J225" s="27" t="n">
         <v>7.5</v>
       </c>
       <c r="K225" s="10" t="n">
@@ -14974,18 +15704,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G226" s="21" t="n">
+      <c r="G226" s="25" t="n">
         <v>7.9</v>
       </c>
       <c r="H226" s="10">
         <f>G226/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I226" s="22">
+      <c r="I226" s="26">
         <f>G226*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J226" s="23" t="n">
+      <c r="J226" s="27" t="n">
         <v>23.3</v>
       </c>
       <c r="K226" s="10" t="n">
@@ -15029,18 +15759,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G227" s="21" t="n">
+      <c r="G227" s="25" t="n">
         <v>6.6</v>
       </c>
       <c r="H227" s="10">
         <f>G227/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I227" s="22">
+      <c r="I227" s="26">
         <f>G227*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J227" s="23" t="n">
+      <c r="J227" s="27" t="n">
         <v>6</v>
       </c>
       <c r="K227" s="10" t="n">
@@ -15080,18 +15810,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G228" s="21" t="n">
+      <c r="G228" s="25" t="n">
         <v>5.7</v>
       </c>
       <c r="H228" s="10">
         <f>G228/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I228" s="22">
+      <c r="I228" s="26">
         <f>G228*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J228" s="23" t="n">
+      <c r="J228" s="27" t="n">
         <v>9.6</v>
       </c>
       <c r="K228" s="10" t="n">
@@ -15135,18 +15865,18 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G229" s="21" t="n">
+      <c r="G229" s="25" t="n">
         <v>4.7</v>
       </c>
       <c r="H229" s="10">
         <f>G229/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I229" s="22">
+      <c r="I229" s="26">
         <f>G229*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J229" s="23" t="n">
+      <c r="J229" s="27" t="n">
         <v>20.8</v>
       </c>
       <c r="K229" s="10" t="n">
@@ -15190,18 +15920,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G230" s="21" t="n">
+      <c r="G230" s="25" t="n">
         <v>4.6</v>
       </c>
       <c r="H230" s="10">
         <f>G230/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I230" s="22">
+      <c r="I230" s="26">
         <f>G230*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J230" s="23" t="n">
+      <c r="J230" s="27" t="n">
         <v>9.1</v>
       </c>
       <c r="K230" s="10" t="n">
@@ -15245,18 +15975,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G231" s="21" t="n">
+      <c r="G231" s="25" t="n">
         <v>4.4</v>
       </c>
       <c r="H231" s="10">
         <f>G231/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I231" s="22">
+      <c r="I231" s="26">
         <f>G231*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J231" s="23" t="n">
+      <c r="J231" s="27" t="n">
         <v>1.8</v>
       </c>
       <c r="K231" s="10" t="n">
@@ -15296,18 +16026,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G232" s="21" t="n">
+      <c r="G232" s="25" t="n">
         <v>4.3</v>
       </c>
       <c r="H232" s="10">
         <f>G232/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I232" s="22">
+      <c r="I232" s="26">
         <f>G232*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J232" s="23" t="n">
+      <c r="J232" s="27" t="n">
         <v>70.7</v>
       </c>
       <c r="K232" s="10" t="n">
@@ -15351,18 +16081,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G233" s="21" t="n">
+      <c r="G233" s="25" t="n">
         <v>4.3</v>
       </c>
       <c r="H233" s="10">
         <f>G233/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I233" s="22">
+      <c r="I233" s="26">
         <f>G233*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J233" s="23" t="n">
+      <c r="J233" s="27" t="n">
         <v>9.4</v>
       </c>
       <c r="K233" s="10" t="n">
@@ -15402,18 +16132,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G234" s="21" t="n">
+      <c r="G234" s="25" t="n">
         <v>4.1</v>
       </c>
       <c r="H234" s="10">
         <f>G234/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I234" s="22">
+      <c r="I234" s="26">
         <f>G234*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J234" s="23" t="n">
+      <c r="J234" s="27" t="n">
         <v>13.2</v>
       </c>
       <c r="K234" s="10" t="n">
@@ -15453,18 +16183,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G235" s="21" t="n">
+      <c r="G235" s="25" t="n">
         <v>3.8</v>
       </c>
       <c r="H235" s="10">
         <f>G235/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I235" s="22">
+      <c r="I235" s="26">
         <f>G235*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J235" s="23" t="n">
+      <c r="J235" s="27" t="n">
         <v>15.2</v>
       </c>
       <c r="K235" s="10" t="n">
@@ -15504,18 +16234,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G236" s="21" t="n">
+      <c r="G236" s="25" t="n">
         <v>3.8</v>
       </c>
       <c r="H236" s="10">
         <f>G236/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I236" s="22">
+      <c r="I236" s="26">
         <f>G236*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J236" s="23" t="n">
+      <c r="J236" s="27" t="n">
         <v>4.2</v>
       </c>
       <c r="K236" s="10" t="n">
@@ -15555,18 +16285,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G237" s="21" t="n">
+      <c r="G237" s="25" t="n">
         <v>3.6</v>
       </c>
       <c r="H237" s="10">
         <f>G237/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I237" s="22">
+      <c r="I237" s="26">
         <f>G237*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J237" s="23" t="n">
+      <c r="J237" s="27" t="n">
         <v>0.9</v>
       </c>
       <c r="K237" s="10" t="n">
@@ -15606,18 +16336,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G238" s="21" t="n">
+      <c r="G238" s="25" t="n">
         <v>3.4</v>
       </c>
       <c r="H238" s="10">
         <f>G238/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I238" s="22">
+      <c r="I238" s="26">
         <f>G238*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J238" s="23" t="n">
+      <c r="J238" s="27" t="n">
         <v>11.6</v>
       </c>
       <c r="K238" s="10" t="n">
@@ -15657,18 +16387,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G239" s="21" t="n">
+      <c r="G239" s="25" t="n">
         <v>3.4</v>
       </c>
       <c r="H239" s="10">
         <f>G239/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I239" s="22">
+      <c r="I239" s="26">
         <f>G239*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J239" s="23" t="n">
+      <c r="J239" s="27" t="n">
         <v>2.7</v>
       </c>
       <c r="K239" s="10" t="n">
@@ -15708,18 +16438,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G240" s="21" t="n">
+      <c r="G240" s="25" t="n">
         <v>2.8</v>
       </c>
       <c r="H240" s="10">
         <f>G240/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I240" s="22">
+      <c r="I240" s="26">
         <f>G240*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J240" s="23" t="n">
+      <c r="J240" s="27" t="n">
         <v>6.5</v>
       </c>
       <c r="K240" s="10" t="n">
@@ -15759,18 +16489,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G241" s="21" t="n">
+      <c r="G241" s="25" t="n">
         <v>2.6</v>
       </c>
       <c r="H241" s="10">
         <f>G241/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I241" s="22">
+      <c r="I241" s="26">
         <f>G241*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J241" s="23" t="n">
+      <c r="J241" s="27" t="n">
         <v>6.3</v>
       </c>
       <c r="K241" s="10" t="n">
@@ -15810,18 +16540,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G242" s="21" t="n">
+      <c r="G242" s="25" t="n">
         <v>2.3</v>
       </c>
       <c r="H242" s="10">
         <f>G242/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I242" s="22">
+      <c r="I242" s="26">
         <f>G242*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J242" s="23" t="n">
+      <c r="J242" s="27" t="n">
         <v>100.2</v>
       </c>
       <c r="K242" s="10" t="n">
@@ -15865,18 +16595,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G243" s="21" t="n">
+      <c r="G243" s="25" t="n">
         <v>1.9</v>
       </c>
       <c r="H243" s="10">
         <f>G243/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I243" s="22">
+      <c r="I243" s="26">
         <f>G243*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J243" s="23" t="n">
+      <c r="J243" s="27" t="n">
         <v>10.1</v>
       </c>
       <c r="K243" s="10" t="n">
@@ -15916,18 +16646,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G244" s="21" t="n">
+      <c r="G244" s="25" t="n">
         <v>1.8</v>
       </c>
       <c r="H244" s="10">
         <f>G244/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I244" s="22">
+      <c r="I244" s="26">
         <f>G244*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J244" s="23" t="n">
+      <c r="J244" s="27" t="n">
         <v>42.8</v>
       </c>
       <c r="K244" s="10" t="n">
@@ -15971,18 +16701,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G245" s="21" t="n">
+      <c r="G245" s="25" t="n">
         <v>1.8</v>
       </c>
       <c r="H245" s="10">
         <f>G245/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I245" s="22">
+      <c r="I245" s="26">
         <f>G245*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J245" s="23" t="n">
+      <c r="J245" s="27" t="n">
         <v>46.6</v>
       </c>
       <c r="K245" s="10" t="n">
@@ -16026,18 +16756,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G246" s="21" t="n">
+      <c r="G246" s="25" t="n">
         <v>1.1</v>
       </c>
       <c r="H246" s="10">
         <f>G246/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I246" s="22">
+      <c r="I246" s="26">
         <f>G246*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J246" s="23" t="n">
+      <c r="J246" s="27" t="n">
         <v>0.7</v>
       </c>
       <c r="K246" s="10" t="n">
@@ -16081,18 +16811,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G247" s="21" t="n">
+      <c r="G247" s="25" t="n">
         <v>0.9</v>
       </c>
       <c r="H247" s="10">
         <f>G247/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I247" s="22">
+      <c r="I247" s="26">
         <f>G247*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J247" s="23" t="n">
+      <c r="J247" s="27" t="n">
         <v>0.9</v>
       </c>
       <c r="K247" s="10" t="n">
@@ -16132,18 +16862,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G248" s="21" t="n">
+      <c r="G248" s="25" t="n">
         <v>0.8</v>
       </c>
       <c r="H248" s="10">
         <f>G248/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I248" s="22">
+      <c r="I248" s="26">
         <f>G248*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J248" s="23" t="n">
+      <c r="J248" s="27" t="n">
         <v>0.8</v>
       </c>
       <c r="K248" s="10" t="n">
@@ -16183,18 +16913,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G249" s="21" t="n">
+      <c r="G249" s="25" t="n">
         <v>0.5</v>
       </c>
       <c r="H249" s="10">
         <f>G249/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I249" s="22">
+      <c r="I249" s="26">
         <f>G249*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J249" s="23" t="n">
+      <c r="J249" s="27" t="n">
         <v>25.2</v>
       </c>
       <c r="K249" s="10" t="n">
@@ -16238,18 +16968,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G250" s="21" t="n">
+      <c r="G250" s="25" t="n">
         <v>0.2</v>
       </c>
       <c r="H250" s="10">
         <f>G250/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I250" s="22">
+      <c r="I250" s="26">
         <f>G250*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J250" s="23" t="n">
+      <c r="J250" s="27" t="n">
         <v>0.8</v>
       </c>
       <c r="K250" s="10" t="n">
@@ -16289,18 +17019,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G251" s="21" t="n">
+      <c r="G251" s="25" t="n">
         <v>0.2</v>
       </c>
       <c r="H251" s="10">
         <f>G251/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I251" s="22">
+      <c r="I251" s="26">
         <f>G251*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J251" s="23" t="n">
+      <c r="J251" s="27" t="n">
         <v>111.3</v>
       </c>
       <c r="K251" s="10" t="n">
@@ -16344,18 +17074,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G252" s="21" t="n">
+      <c r="G252" s="25" t="n">
         <v>0.1</v>
       </c>
       <c r="H252" s="10">
         <f>G252/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I252" s="22">
+      <c r="I252" s="26">
         <f>G252*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J252" s="23" t="n">
+      <c r="J252" s="27" t="n">
         <v>0.3</v>
       </c>
       <c r="K252" s="10" t="n">
@@ -16395,18 +17125,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G253" s="21" t="n">
+      <c r="G253" s="25" t="n">
         <v>0.1</v>
       </c>
       <c r="H253" s="10">
         <f>G253/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I253" s="22">
+      <c r="I253" s="26">
         <f>G253*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J253" s="23" t="n">
+      <c r="J253" s="27" t="n">
         <v>0.7</v>
       </c>
       <c r="K253" s="10" t="n">
@@ -16446,18 +17176,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G254" s="21" t="n">
+      <c r="G254" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H254" s="10">
         <f>G254/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I254" s="22">
+      <c r="I254" s="26">
         <f>G254*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J254" s="23" t="n">
+      <c r="J254" s="27" t="n">
         <v>20.8</v>
       </c>
       <c r="K254" s="10" t="n">
@@ -16501,18 +17231,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G255" s="21" t="n">
+      <c r="G255" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H255" s="10">
         <f>G255/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I255" s="22">
+      <c r="I255" s="26">
         <f>G255*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J255" s="23" t="n">
+      <c r="J255" s="27" t="n">
         <v>26.2</v>
       </c>
       <c r="K255" s="10" t="n">
@@ -16556,18 +17286,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G256" s="21" t="n">
+      <c r="G256" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H256" s="10">
         <f>G256/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I256" s="22">
+      <c r="I256" s="26">
         <f>G256*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J256" s="23" t="n">
+      <c r="J256" s="27" t="n">
         <v>47.7</v>
       </c>
       <c r="K256" s="10" t="n">
@@ -16611,18 +17341,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G257" s="21" t="n">
+      <c r="G257" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H257" s="10">
         <f>G257/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I257" s="22">
+      <c r="I257" s="26">
         <f>G257*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J257" s="23" t="n">
+      <c r="J257" s="27" t="n">
         <v>46.9</v>
       </c>
       <c r="K257" s="10" t="n">
@@ -16666,18 +17396,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G258" s="21" t="n">
+      <c r="G258" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H258" s="10">
         <f>G258/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I258" s="22">
+      <c r="I258" s="26">
         <f>G258*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J258" s="23" t="n">
+      <c r="J258" s="27" t="n">
         <v>14</v>
       </c>
       <c r="K258" s="10" t="n">
@@ -16721,18 +17451,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G259" s="21" t="n">
+      <c r="G259" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H259" s="10">
         <f>G259/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I259" s="22">
+      <c r="I259" s="26">
         <f>G259*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J259" s="23" t="n">
+      <c r="J259" s="27" t="n">
         <v>10.8</v>
       </c>
       <c r="K259" s="10" t="n">
@@ -16776,18 +17506,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G260" s="21" t="n">
+      <c r="G260" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H260" s="10">
         <f>G260/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I260" s="22">
+      <c r="I260" s="26">
         <f>G260*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J260" s="23" t="n">
+      <c r="J260" s="27" t="n">
         <v>7.6</v>
       </c>
       <c r="K260" s="10" t="n">
@@ -16827,18 +17557,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G261" s="21" t="n">
+      <c r="G261" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H261" s="10">
         <f>G261/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I261" s="22">
+      <c r="I261" s="26">
         <f>G261*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J261" s="23" t="n">
+      <c r="J261" s="27" t="n">
         <v>23.6</v>
       </c>
       <c r="K261" s="10" t="n">
@@ -16878,18 +17608,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G262" s="21" t="n">
+      <c r="G262" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H262" s="10">
         <f>G262/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I262" s="22">
+      <c r="I262" s="26">
         <f>G262*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J262" s="23" t="n">
+      <c r="J262" s="27" t="n">
         <v>7.1</v>
       </c>
       <c r="K262" s="10" t="n">
@@ -16929,18 +17659,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G263" s="21" t="n">
+      <c r="G263" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H263" s="10">
         <f>G263/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I263" s="22">
+      <c r="I263" s="26">
         <f>G263*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J263" s="23" t="n">
+      <c r="J263" s="27" t="n">
         <v>15.7</v>
       </c>
       <c r="K263" s="10" t="n">
@@ -16984,18 +17714,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G264" s="21" t="n">
+      <c r="G264" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H264" s="10">
         <f>G264/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I264" s="22">
+      <c r="I264" s="26">
         <f>G264*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J264" s="23" t="n">
+      <c r="J264" s="27" t="n">
         <v>31.4</v>
       </c>
       <c r="K264" s="10" t="n">
@@ -17039,18 +17769,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G265" s="21" t="n">
+      <c r="G265" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H265" s="10">
         <f>G265/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I265" s="22">
+      <c r="I265" s="26">
         <f>G265*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J265" s="23" t="n">
+      <c r="J265" s="27" t="n">
         <v>24.6</v>
       </c>
       <c r="K265" s="10" t="n">
@@ -17094,18 +17824,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G266" s="21" t="n">
+      <c r="G266" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H266" s="10">
         <f>G266/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I266" s="22">
+      <c r="I266" s="26">
         <f>G266*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J266" s="23" t="n">
+      <c r="J266" s="27" t="n">
         <v>0.4</v>
       </c>
       <c r="K266" s="10" t="n">
@@ -17145,18 +17875,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G267" s="21" t="n">
+      <c r="G267" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H267" s="10">
         <f>G267/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I267" s="22">
+      <c r="I267" s="26">
         <f>G267*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J267" s="23" t="n">
+      <c r="J267" s="27" t="n">
         <v>2.5</v>
       </c>
       <c r="K267" s="10" t="n">
@@ -17196,18 +17926,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G268" s="21" t="n">
+      <c r="G268" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H268" s="10">
         <f>G268/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I268" s="22">
+      <c r="I268" s="26">
         <f>G268*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J268" s="23" t="n">
+      <c r="J268" s="27" t="n">
         <v>0.8</v>
       </c>
       <c r="K268" s="10" t="n">
@@ -17247,18 +17977,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G269" s="21" t="n">
+      <c r="G269" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H269" s="10">
         <f>G269/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I269" s="22">
+      <c r="I269" s="26">
         <f>G269*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J269" s="23" t="n">
+      <c r="J269" s="27" t="n">
         <v>0</v>
       </c>
       <c r="K269" s="10" t="n">
@@ -17298,18 +18028,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G270" s="21" t="n">
+      <c r="G270" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H270" s="10">
         <f>G270/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I270" s="22">
+      <c r="I270" s="26">
         <f>G270*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J270" s="23" t="n">
+      <c r="J270" s="27" t="n">
         <v>0</v>
       </c>
       <c r="K270" s="10" t="n">
@@ -17349,18 +18079,18 @@
           <t>L</t>
         </is>
       </c>
-      <c r="G271" s="21" t="n">
+      <c r="G271" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H271" s="10">
         <f>G271/Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I271" s="22">
+      <c r="I271" s="26">
         <f>G271*1000*Assumptions!$B$8/1000000</f>
         <v/>
       </c>
-      <c r="J271" s="23" t="n">
+      <c r="J271" s="27" t="n">
         <v>7.4</v>
       </c>
       <c r="K271" s="10" t="n">
@@ -17407,7 +18137,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17471,7 +18201,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>THE TWO HIGHEST-LEVERAGE CALLS IN THE WHOLE EXERCISE</t>
         </is>
@@ -17547,7 +18277,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>THE ABEEÓLICA BOARD ROSTER — each member company's own regulatory representative</t>
         </is>
@@ -17591,7 +18321,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>THE CURTAILMENT OWNER AT EACH MAJOR GENERATOR — call these, not the CEO</t>
         </is>
@@ -17955,7 +18685,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="24" t="inlineStr">
+      <c r="A22" s="28" t="inlineStr">
         <is>
           <t>FINANCE — for when the conversation turns to the cash-versus-book-entry question</t>
         </is>
@@ -18095,7 +18825,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="24" t="inlineStr">
+      <c r="A27" s="28" t="inlineStr">
         <is>
           <t>THE OTHER ASSOCIATION, AND THE REGIONAL VOICES</t>
         </is>
@@ -18203,7 +18933,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="24" t="inlineStr">
+      <c r="A31" s="28" t="inlineStr">
         <is>
           <t>HOW TO USE THIS SHEET</t>
         </is>
@@ -18230,7 +18960,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="D32" s="25" t="inlineStr">
+      <c r="D32" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -18262,7 +18992,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="D33" s="25" t="inlineStr">
+      <c r="D33" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -18294,7 +19024,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="D34" s="25" t="inlineStr">
+      <c r="D34" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -18326,7 +19056,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="D35" s="25" t="inlineStr">
+      <c r="D35" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -18347,7 +19077,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18399,7 +19129,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>INPUTS — edit the yellow cells; every estimate on the other tabs recalculates</t>
         </is>
@@ -18414,7 +19144,7 @@
           <t>Compensation pool, Portaria 140 window</t>
         </is>
       </c>
-      <c r="B6" s="26" t="n">
+      <c r="B6" s="30" t="n">
         <v>3300</v>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -18434,7 +19164,7 @@
           <t>Eligible curtailment in the window</t>
         </is>
       </c>
-      <c r="B7" s="26" t="n">
+      <c r="B7" s="30" t="n">
         <v>25326</v>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -18454,7 +19184,7 @@
           <t>Implied compensation price</t>
         </is>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="31">
         <f>B6/B7*1000</f>
         <v/>
       </c>
@@ -18474,7 +19204,7 @@
           <t>IPCA uplift, event date to payment</t>
         </is>
       </c>
-      <c r="B9" s="28" t="n">
+      <c r="B9" s="32" t="n">
         <v>0.22</v>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -18494,7 +19224,7 @@
           <t>Sutphin fee on an advisory mandate</t>
         </is>
       </c>
-      <c r="B10" s="28" t="n">
+      <c r="B10" s="32" t="n">
         <v>0.015</v>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -18509,13 +19239,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="inlineStr"/>
+      <c r="A11" s="28" t="inlineStr"/>
       <c r="B11" s="15" t="inlineStr"/>
       <c r="C11" s="15" t="inlineStr"/>
       <c r="D11" s="15" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="24" t="inlineStr">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>WHAT THIS MODEL DELIBERATELY DOES NOT DO</t>
         </is>
@@ -18525,7 +19255,7 @@
       <c r="D12" s="15" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="A13" s="28" t="inlineStr">
         <is>
           <t>It does not split cash from book entry</t>
         </is>
@@ -18535,7 +19265,7 @@
       <c r="D13" s="15" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="24" t="inlineStr">
+      <c r="A14" s="28" t="inlineStr">
         <is>
           <t>It does not net against what they owe CCEE</t>
         </is>
@@ -18545,7 +19275,7 @@
       <c r="D14" s="15" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="24" t="inlineStr">
+      <c r="A15" s="28" t="inlineStr">
         <is>
           <t>It does not price the waiver</t>
         </is>
@@ -18555,7 +19285,7 @@
       <c r="D15" s="15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="24" t="inlineStr">
+      <c r="A16" s="28" t="inlineStr">
         <is>
           <t>It does not value the garantia física BENEFIT</t>
         </is>
@@ -18565,7 +19295,7 @@
       <c r="D16" s="15" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="24" t="inlineStr">
+      <c r="A17" s="28" t="inlineStr">
         <is>
           <t>It uses one price for everyone</t>
         </is>
@@ -18579,7 +19309,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18625,7 +19355,7 @@
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>THE INSTRUMENT</t>
         </is>
@@ -18736,7 +19466,7 @@
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="24" t="inlineStr">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>DATES</t>
         </is>
@@ -18881,7 +19611,7 @@
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="24" t="inlineStr">
+      <c r="A21" s="28" t="inlineStr">
         <is>
           <t>WHO IS ELIGIBLE</t>
         </is>
@@ -18967,7 +19697,7 @@
       <c r="C26" s="7" t="inlineStr"/>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="24" t="inlineStr">
+      <c r="A27" s="28" t="inlineStr">
         <is>
           <t>WHAT IS PAID FOR</t>
         </is>
@@ -19078,7 +19808,7 @@
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="24" t="inlineStr">
+      <c r="A34" s="28" t="inlineStr">
         <is>
           <t>HOW IT IS VALUED — THE WATERFALL</t>
         </is>
@@ -19206,7 +19936,7 @@
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="24" t="inlineStr">
+      <c r="A42" s="28" t="inlineStr">
         <is>
           <t>WHO ACTUALLY PAYS</t>
         </is>
@@ -19266,7 +19996,7 @@
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="24" t="inlineStr">
+      <c r="A46" s="28" t="inlineStr">
         <is>
           <t>THE WAIVER — READ THIS TWICE</t>
         </is>
@@ -19411,7 +20141,7 @@
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="24" t="inlineStr">
+      <c r="A55" s="28" t="inlineStr">
         <is>
           <t>TRAPS</t>
         </is>
@@ -19522,7 +20252,7 @@
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
-      <c r="A62" s="24" t="inlineStr">
+      <c r="A62" s="28" t="inlineStr">
         <is>
           <t>THE FOUR STEPS A GENERATOR MUST TAKE</t>
         </is>
@@ -19603,7 +20333,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19639,7 +20369,7 @@
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>THE SINGLE MOST IMPORTANT THING TO UNDERSTAND — AND ALMOST NOBODY HAS</t>
         </is>
@@ -19667,7 +20397,7 @@
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>THE OPENING — 20 SECONDS</t>
         </is>
@@ -19699,7 +20429,7 @@
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="24" t="inlineStr">
+      <c r="A11" s="28" t="inlineStr">
         <is>
           <t>THE FOUR THINGS ACTUALLY WORTH MONEY TO THEM</t>
         </is>
@@ -19755,7 +20485,7 @@
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="24" t="inlineStr">
+      <c r="A16" s="28" t="inlineStr">
         <is>
           <t>THE TWO STRUCTURAL POINTS TO HAVE READY</t>
         </is>
@@ -19787,7 +20517,7 @@
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="24" t="inlineStr">
+      <c r="A19" s="28" t="inlineStr">
         <is>
           <t>WHAT YOU ARE OFFERING ON CALL ONE</t>
         </is>
@@ -19819,7 +20549,7 @@
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="24" t="inlineStr">
+      <c r="A22" s="28" t="inlineStr">
         <is>
           <t>WHAT YOU DO NOT SAY ON CALL ONE</t>
         </is>
@@ -19875,7 +20605,7 @@
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="24" t="inlineStr">
+      <c r="A27" s="28" t="inlineStr">
         <is>
           <t>WHERE THE CAPITAL ACTUALLY GOES</t>
         </is>
@@ -19931,7 +20661,7 @@
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="24" t="inlineStr">
+      <c r="A32" s="28" t="inlineStr">
         <is>
           <t>HANDLING THE OBVIOUS PUSHBACKS</t>
         </is>
@@ -19991,7 +20721,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -20037,7 +20767,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>PRIMARY — THE INSTRUMENT</t>
         </is>
@@ -20056,7 +20786,7 @@
           <t>DOU 21/07/2026, Ed. 135-A, Seção 1 Extra A, p.10</t>
         </is>
       </c>
-      <c r="C6" s="29" t="inlineStr">
+      <c r="C6" s="33" t="inlineStr">
         <is>
           <t>https://www.in.gov.br/web/dou/-/portaria-normativa-mme-n-140-de-18-de-julho-de-2026-720529777</t>
         </is>
@@ -20073,7 +20803,7 @@
           <t>gov.br/mme</t>
         </is>
       </c>
-      <c r="C7" s="29" t="inlineStr">
+      <c r="C7" s="33" t="inlineStr">
         <is>
           <t>https://www.gov.br/mme/pt-br/assuntos/noticias/mme-regulamenta-procedimentos-para-celebracao-de-termo-de-compromisso-sobre-compensacao-por-cortes-de-geracao</t>
         </is>
@@ -20090,7 +20820,7 @@
           <t>Where the manifestação de interesse is filed by 10 Aug 2026</t>
         </is>
       </c>
-      <c r="C8" s="29" t="inlineStr">
+      <c r="C8" s="33" t="inlineStr">
         <is>
           <t>https://celebra.mme.gov.br/</t>
         </is>
@@ -20107,7 +20837,7 @@
           <t>Inserted by Lei 15.269/2025 — the statutory basis</t>
         </is>
       </c>
-      <c r="C9" s="29" t="inlineStr">
+      <c r="C9" s="33" t="inlineStr">
         <is>
           <t>https://www.planalto.gov.br/ccivil_03/_ato2004-2006/2004/lei/l10.848.htm</t>
         </is>
@@ -20124,7 +20854,7 @@
           <t>Sanctioned 24 Nov 2025, published 25 Nov 2025</t>
         </is>
       </c>
-      <c r="C10" s="29" t="inlineStr">
+      <c r="C10" s="33" t="inlineStr">
         <is>
           <t>https://www.planalto.gov.br/ccivil_03/_ato2023-2026/2025/lei/L15269.htm</t>
         </is>
@@ -20141,7 +20871,7 @@
           <t>The vetoed art. 1º-A — STILL NOT VOTED BY CONGRESS</t>
         </is>
       </c>
-      <c r="C11" s="29" t="inlineStr">
+      <c r="C11" s="33" t="inlineStr">
         <is>
           <t>https://www.planalto.gov.br/ccivil_03/_ato2023-2026/2025/Msg/Vep/VEP-1755-25.htm</t>
         </is>
@@ -20158,14 +20888,14 @@
           <t>Diretora Agnes Maria de Aragão da Costa, Jan 2026. Authoritative source for the 46% ENE / 41% CNF / 13% REL split</t>
         </is>
       </c>
-      <c r="C12" s="29" t="inlineStr">
+      <c r="C12" s="33" t="inlineStr">
         <is>
           <t>https://canalsolar.com.br/wp-content/uploads/2026/01/voto.pdf</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="A13" s="28" t="inlineStr">
         <is>
           <t>DATA — COMPUTED FOR THIS ANALYSIS</t>
         </is>
@@ -20184,7 +20914,7 @@
           <t>Half-hourly, Oct 2021 → Jul 2026, CC-BY. The eligible-claim column is built from this.</t>
         </is>
       </c>
-      <c r="C14" s="29" t="inlineStr">
+      <c r="C14" s="33" t="inlineStr">
         <is>
           <t>https://dados.ons.org.br/dataset/restricao_coff_eolica_usi</t>
         </is>
@@ -20201,7 +20931,7 @@
           <t>1,053 individual plants with CEG — the ownership join</t>
         </is>
       </c>
-      <c r="C15" s="29" t="inlineStr">
+      <c r="C15" s="33" t="inlineStr">
         <is>
           <t>https://dados.ons.org.br/dataset/restricao_coff_eolica_detail</t>
         </is>
@@ -20218,7 +20948,7 @@
           <t>SERIES STARTS APRIL 2024 — there is no public solar curtailment data before that</t>
         </is>
       </c>
-      <c r="C16" s="29" t="inlineStr">
+      <c r="C16" s="33" t="inlineStr">
         <is>
           <t>https://dados.ons.org.br/dataset/restricao_coff_fotovoltaica</t>
         </is>
@@ -20235,7 +20965,7 @@
           <t>Ownership and capacity by CEG. 98.9% of the CEGs in the ONS detail files matched.</t>
         </is>
       </c>
-      <c r="C17" s="29" t="inlineStr">
+      <c r="C17" s="33" t="inlineStr">
         <is>
           <t>https://dadosabertos.aneel.gov.br/dataset/siga-sistema-de-informacoes-de-geracao-da-aneel</t>
         </is>
@@ -20252,7 +20982,7 @@
           <t>Includes an ENCARGO_CONSTRAINED_OFF column, monthly 202311→202605</t>
         </is>
       </c>
-      <c r="C18" s="29" t="inlineStr">
+      <c r="C18" s="33" t="inlineStr">
         <is>
           <t>https://dadosabertos.ccee.org.br/dataset/encargo_recebido_perfil_agente_usina</t>
         </is>
@@ -20269,14 +20999,14 @@
           <t>Nordeste monthly average: 2024 R$118.34 · 2025 R$176.60 · 2026 YTD R$226.63. Floor 2026 R$57.31.</t>
         </is>
       </c>
-      <c r="C19" s="29" t="inlineStr">
+      <c r="C19" s="33" t="inlineStr">
         <is>
           <t>https://dadosabertos.ccee.org.br/dataset/pld_horario</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="24" t="inlineStr">
+      <c r="A20" s="28" t="inlineStr">
         <is>
           <t>SIZING — THE COMPETING ESTIMATES</t>
         </is>
@@ -20295,7 +21025,7 @@
           <t>Poder360, 22 Jul 2026. NO PRIMARY DOCUMENT STATES ANY POOL FIGURE.</t>
         </is>
       </c>
-      <c r="C21" s="29" t="inlineStr">
+      <c r="C21" s="33" t="inlineStr">
         <is>
           <t>https://www.poder360.com.br/poder-governo/governo-regulamenta-acordo-de-r-33-bi-com-usinas-renovaveis/</t>
         </is>
@@ -20312,7 +21042,7 @@
           <t>eixos / MegaWhat, 23 Jul 2026. Found MME's SOSIN formula produces 143% more sobreoferta than ONS's own method.</t>
         </is>
       </c>
-      <c r="C22" s="29" t="inlineStr">
+      <c r="C22" s="33" t="inlineStr">
         <is>
           <t>https://eixos.com.br/politica/volt-robotics-estima-ressarcimento-por-cortes-de-geracao-em-r-27-bilhoes-e-aponta-falta-de-clareza-na-classificacao/</t>
         </is>
@@ -20329,7 +21059,7 @@
           <t>Senate CI hearing, 30 Sep 2025. Best-documented independent methodology.</t>
         </is>
       </c>
-      <c r="C23" s="29" t="inlineStr">
+      <c r="C23" s="33" t="inlineStr">
         <is>
           <t>https://acendebrasil.com.br/wp-content/uploads/2025/09/20250930_AcendeBr_AP_CI_Senado_Curtailment_rev_3-1.pdf</t>
         </is>
@@ -20346,7 +21076,7 @@
           <t>Jan 2026</t>
         </is>
       </c>
-      <c r="C24" s="29" t="inlineStr">
+      <c r="C24" s="33" t="inlineStr">
         <is>
           <t>https://cenarioenergia.com.br/wp-content/uploads/2026/01/VoltRobotics_AnaliseCurtailment_Balanco-2025_Janeiro-2026.pdf</t>
         </is>
@@ -20363,14 +21093,14 @@
           <t>Auren R$400m · Serena R$200m · Engie Brasil R$150m. Via NeoFeed, 25 Feb 2026.</t>
         </is>
       </c>
-      <c r="C25" s="29" t="inlineStr">
+      <c r="C25" s="33" t="inlineStr">
         <is>
           <t>https://neofeed.com.br/negocios/brasil-desperdica-20-de-sua-energia-renovavel-e-gera-prejuizos-bilionarios-a-empresas-do-setor-eletrico/</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="24" t="inlineStr">
+      <c r="A26" s="28" t="inlineStr">
         <is>
           <t>LITIGATION</t>
         </is>
@@ -20389,7 +21119,7 @@
           <t>MegaWhat, 31 Oct 2024. None had obtained a liminar.</t>
         </is>
       </c>
-      <c r="C27" s="29" t="inlineStr">
+      <c r="C27" s="33" t="inlineStr">
         <is>
           <t>https://megawhat.energy/geracao/aneel-ja-e-alvo-de-12-acoes-judiciais-por-curtailment/</t>
         </is>
@@ -20406,7 +21136,7 @@
           <t>SLS 3.546, Min. Herman Benjamin, Jan 2025</t>
         </is>
       </c>
-      <c r="C28" s="29" t="inlineStr">
+      <c r="C28" s="33" t="inlineStr">
         <is>
           <t>https://www.arandanet.com.br/revista/em/noticia/10214-Aneel-consegue-suspender-liminar-do-constrained-off-no-STJ.html</t>
         </is>
@@ -20423,7 +21153,7 @@
           <t>Canal Solar, 17 Jun 2026 — STILL UNVOTED as at 26 Jul 2026</t>
         </is>
       </c>
-      <c r="C29" s="29" t="inlineStr">
+      <c r="C29" s="33" t="inlineStr">
         <is>
           <t>https://canalsolar.com.br/congresso-analisa-vetos-regras-gd-eolicas-offshore/</t>
         </is>
@@ -20440,14 +21170,14 @@
           <t>eixos, 23 Jul 2026</t>
         </is>
       </c>
-      <c r="C30" s="29" t="inlineStr">
+      <c r="C30" s="33" t="inlineStr">
         <is>
           <t>https://eixos.com.br/energias-renovaveis/portaria-traz-alivio-mas-nao-encerra-judicializacao-sobre-cortes-de-geracao-avaliam-geradores-e-especialistas/</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="24" t="inlineStr">
+      <c r="A31" s="28" t="inlineStr">
         <is>
           <t>COMPANY DISCLOSURE</t>
         </is>
@@ -20466,7 +21196,7 @@
           <t>THE FIRST REALISED COMPENSATION FIGURE IN THE MARKET. MegaWhat, 23 Jul 2026.</t>
         </is>
       </c>
-      <c r="C32" s="29" t="inlineStr">
+      <c r="C32" s="33" t="inlineStr">
         <is>
           <t>https://megawhat.uol.com.br/economia-e-politica/resultados/voltalia-contabiliza-r-175-mi-em-ressarcimento-do-curtailment-no-resultado-do-2o-tri/</t>
         </is>
@@ -20483,7 +21213,7 @@
           <t>CPFL 4T25 release. The most transparent disclosure in the sector.</t>
         </is>
       </c>
-      <c r="C33" s="29" t="inlineStr">
+      <c r="C33" s="33" t="inlineStr">
         <is>
           <t>https://ri.cpfl.com.br/</t>
         </is>
@@ -20500,7 +21230,7 @@
           <t>Worst assets: Santo Agostinho 36%, Trairi 31%, Campo Largo 17%, Serra do Assuruá 14%</t>
         </is>
       </c>
-      <c r="C34" s="29" t="inlineStr">
+      <c r="C34" s="33" t="inlineStr">
         <is>
           <t>https://www.engie.com.br/wp-content/uploads/2026/02/260225-Release-de-Resultados-4T25.pdf</t>
         </is>
@@ -20517,7 +21247,7 @@
           <t>FY2025 gross R$529.5m, R$333.6m net of modulation gains</t>
         </is>
       </c>
-      <c r="C35" s="29" t="inlineStr">
+      <c r="C35" s="33" t="inlineStr">
         <is>
           <t>https://ri.auren.com.br/</t>
         </is>
